--- a/datasets/AU_attributes/aposteriori_unimodal_attitudes.race.xlsx
+++ b/datasets/AU_attributes/aposteriori_unimodal_attitudes.race.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,85 +441,80 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>toany</t>
+          <t>annotatorMinority</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>annotatorMinority</t>
+          <t>annotatorPolitics</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>bert</t>
+          <t>traditionalism</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>annotatorPolitics</t>
+          <t>annotatorRace</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>traditionalism</t>
+          <t>annotatorAge</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>annotatorRace</t>
+          <t>annotatorGender</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>annotatorAge</t>
+          <t>freeSpeech</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>annotatorGender</t>
+          <t>harmHateSpeech</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>freeSpeech</t>
+          <t>intent</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>harmHateSpeech</t>
+          <t>lingPurism</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>intent</t>
+          <t>racism</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>lingPurism</t>
+          <t>racist</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>racism</t>
+          <t>annotator_count</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>racist</t>
+          <t>scores</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>scores</t>
+          <t>HIST</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>HIST</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>DFU</t>
         </is>
@@ -541,85 +536,78 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[4, 5, 2, 2, 2, 2]</t>
+          <t>['{}', '{}', '{}', '{}', '{}', '{}']</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['{}', '{}', '{}', '{}', '{}', '{}']</t>
+          <t>['left', 'far left', 'center', 'right', 'left', 'left']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[0.09306392818689346, -0.14795063436031342, 0.41057923436164856, 0.03671635314822197, -0.5124063491821289, -0.24005286395549774, 0.4842818081378937, 0.672923743724823, 0.11185003072023392, -0.3239098787307739, 0.1603410243988037, 0.04533151537179947, 0.05676272138953209, 0.6116381883621216, -0.23225313425064087, -0.027103139087557793, -0.10728247463703156, 0.27259141206741333, -0.07017216086387634, 0.15866133570671082, 0.39964330196380615, -0.22783057391643524, 0.20263059437274933, -0.18151573836803436, -0.05705397203564644, 0.1317632794380188, 0.20164060592651367, 0.34197667241096497, 0.0383225716650486, 0.2208104133605957, 0.17746689915657043, 0.16049824655056, -0.3069741725921631, 0.42983734607696533, -0.12384837865829468, -0.24547399580478668, 0.29908356070518494, 0.17392444610595703, 0.27349063754081726, -0.22186525166034698, -0.3012089431285858, -0.1574801504611969, -0.22745025157928467, -0.27571964263916016, -0.5502662658691406, -0.3229992687702179, -3.344940185546875, 0.06447747349739075, -0.06045407056808472, -0.6935566663742065, 0.42915573716163635, -0.2558894753456116, 0.0018420207779854536, 0.40674030780792236, 0.505827009677887, 0.23404476046562195, -0.3043626844882965, -0.42004507780075073, -0.2152082473039627, 0.2659592926502228, 0.7764633893966675, 0.00866306759417057, -0.2267722487449646, 0.36513832211494446, -0.10379692912101746, 0.1882607787847519, -0.2888619303703308, 0.22780631482601166, -0.40394097566604614, 0.3299020826816559, -0.2748607397079468, -0.08076272904872894, 0.6720553040504456, 0.17024140059947968, -0.05224769935011864, -0.3795003890991211, -0.3307211697101593, 0.3769418001174927, 0.2605911195278168, -0.011694070883095264, 0.11925148963928223, -0.13304753601551056, 0.3032833933830261, 0.02509557269513607, -0.04912000522017479, 0.5881587862968445, -0.146118625998497, -0.30234038829803467, -0.16557054221630096, 0.14938588440418243, 0.009405465796589851, 0.3298299014568329, -0.07123873382806778, 0.5120888352394104, 0.37075814604759216, 0.10412076115608215, -0.10667365044355392, 0.10390332341194153, 0.02759326435625553, 0.7332736253738403, -0.09131785482168198, 0.19392623007297516, 0.09574287384748459, -0.15859729051589966, 0.04237302765250206, -0.20590844750404358, -0.1292387694120407, 0.12419363856315613, 0.16574370861053467, -1.9072858095169067, 0.08881119638681412, 0.13570350408554077, 0.25164103507995605, -0.2016260176897049, -0.7175509333610535, -0.1504911184310913, 0.4823032319545746, 0.11961644887924194, 0.6102478504180908, 0.3832698166370392, -0.4073178768157959, 0.08195114880800247, 0.476071834564209, 0.05919494852423668, 0.58585524559021, 0.15572699904441833, -0.5276182293891907, -0.4271482825279236, -0.10273649543523788, 0.570205569267273, 0.2261098027229309, 0.5083884000778198, 0.010296730324625969, 0.24837295711040497, -0.2123410701751709, 0.05919361487030983, 0.33839789032936096, -0.6681329607963562, 0.11235738545656204, -0.12019205838441849, -0.43398791551589966, -0.2898732125759125, -2.5881450176239014, 0.7759324312210083, 0.2720792293548584, 0.16761064529418945, -0.44823595881462097, -0.19260399043560028, -0.16193178296089172, 0.0995461568236351, 0.0903199315071106, 0.06506601721048355, -0.4890691041946411, -0.0880536362528801, -0.4490339159965515, 0.08154574036598206, -0.5018619894981384, -0.08498097956180573, 0.1027609258890152, 0.945896565914154, -0.3262803554534912, -0.34479084610939026, -0.31392601132392883, -0.2562057077884674, -0.20017369091510773, -0.48928582668304443, 0.2757335305213928, 0.7072086334228516, -0.17041049897670746, -0.4296604096889496, -0.2889919579029083, 0.15059763193130493, 0.26882508397102356, 0.26947543025016785, 0.22400197386741638, -0.22479626536369324, 0.3262432813644409, 0.3114020526409149, -0.1504010260105133, 0.03881056234240532, -0.4422226548194885, 0.42924466729164124, 0.058706361800432205, 0.3978811800479889, 0.06542600691318512, -0.29850688576698303, 0.4400160312652588, 0.22440160810947418, -0.22306807339191437, 0.053329311311244965, -0.6066147089004517, -0.09361354261636734, 0.53387850522995, 0.6085676550865173, 0.839773952960968, -0.42681047320365906, 0.3471134901046753, -0.4525039494037628, 0.4039609432220459, 0.1706799566745758, 0.25631996989250183, -0.09129473567008972, 0.13398665189743042, -0.1217423751950264, -0.12817534804344177, 3.7176661491394043, 0.33463022112846375, 0.2544924318790436, 0.3991265296936035, 0.47774583101272583, 0.26949524879455566, 0.2808474600315094, -0.3088814616203308, 0.04581208527088165, -0.11651372909545898, -0.5449659824371338, -0.10048898309469223, -0.009875715710222721, -0.2742002010345459, 0.19988952577114105, 0.11951721459627151, 0.28730788826942444, -0.6396461725234985, 0.49920716881752014, -0.3195074200630188, -0.4709758460521698, 0.1228775754570961, -0.16995716094970703, 0.3103698194026947, -1.4969700574874878, 0.15811222791671753, -0.2318728268146515, -0.3034047484397888, 0.1277816742658615, -0.24946479499340057, 0.4207399785518646, 0.3405400216579437, 0.310846209526062, 0.10763239860534668, 0.10018224269151688, -0.12991148233413696, 0.5095647573471069, 0.08128178119659424, -0.0611608661711216, 0.0966973528265953, 0.9629021883010864, -0.19376154243946075, -0.7603779435157776, -0.3176857829093933, -0.08898462355136871, 0.3077557682991028, -0.12136269360780716, 0.5424553751945496, -0.31692689657211304, -0.07522329688072205, -0.2909814715385437, 0.03199567645788193, -0.47235730290412903, -0.07741521298885345, -0.569234311580658, -0.27355632185935974, 0.3097001910209656, 0.09533862769603729, 0.02842727303504944, -0.28633537888526917, -0.4094942808151245, 0.2546859681606293, -0.07407791912555695, -0.16303665935993195, -0.03830462694168091, -0.06326750665903091, -0.10853704810142517, -0.014890331774950027, -2.553314447402954, 0.27511245012283325, -0.28117260336875916, -0.0912376269698143, 0.2641772925853729, -0.10522093623876572, 0.10225586593151093, 0.048850253224372864, 0.39906400442123413, -0.4219167232513428, 0.2940133810043335, 0.10872456431388855, 0.1910426914691925, -0.018448052927851677, -0.23884901404380798, 0.23616033792495728, -0.14548814296722412, 0.3418561518192291, -0.5017200112342834, 0.22297285497188568, 0.6360175609588623, 0.24644657969474792, -0.5261291265487671, 0.14870157837867737, 0.134598970413208, -0.05649760365486145, -0.4462783634662628, -0.29891252517700195, 0.7731034159660339, 0.23575042188167572, 0.519391655921936, 0.08780301362276077, 0.040773287415504456, -0.1374245584011078, -0.1259385198354721, -4.110198020935059, -0.2648164629936218, -0.3074896037578583, -0.3653579354286194, 0.25417619943618774, -0.14075028896331787, 0.1784788817167282, -0.5420681834220886, -0.42601004242897034, 0.17468132078647614, 0.3610171675682068, 0.2337169647216797, 0.28057485818862915, 0.07629252225160599, 0.10967141389846802, 0.21832787990570068, 0.14773234724998474, -0.2282697707414627, -0.28084537386894226, 0.049816813319921494, -0.031162260100245476, 0.3194481432437897, 0.12985463440418243, -0.09703578054904938, 0.3554971516132355, -0.17545919120311737, -0.11429091542959213, -0.05439949780702591, -0.19278620183467865, 0.28001806139945984, -0.295475035905838, 0.3448420763015747, -0.014088587835431099, -0.4999296963214874, -0.04547011852264404, -0.03775559738278389, 0.3878788948059082, 0.5461922883987427, 0.214824378490448, 0.25491848587989807, 0.09139909595251083, -0.23733261227607727, -0.35980096459388733, -0.260156512260437, 0.10671861469745636, -0.4741077125072479, -0.23065508902072906, -0.21321295201778412, -0.41777122020721436, 0.30061256885528564, 0.5035592913627625, -0.23812641203403473, 0.9327062368392944, -0.2794072926044464, -0.019483285024762154, -0.2613542675971985, 0.367792010307312, 0.33447131514549255, -0.5946088433265686, -0.16528375446796417, 0.3198021948337555, -0.20938831567764282, -0.34583860635757446, -0.24757151305675507, -0.2785649299621582, 0.08949905633926392, 0.5047813057899475, -0.68480384349823, 0.21258233487606049, 0.086387038230896, -0.3625510632991791, 0.22243891656398773, -0.2728704512119293, -1.4124395847320557, 0.2107463926076889, 0.22916021943092346, -0.5083168745040894, 0.09228260815143585, 0.008591749705374241, -0.0011410245206207037, 0.3684921860694885, 0.06161687150597572, 0.008581523783504963, 0.05873960256576538, -0.5429778099060059, -0.7684679627418518, 0.08138322085142136, 0.04878097027540207, -0.8032521605491638, 0.14359347522258759, 0.3034912049770355, 0.03897801786661148, 0.7470173239707947, -0.06757792085409164, 0.6973827481269836, 0.14773252606391907, 0.4382200837135315, -0.7887865900993347, -0.08012572675943375, -0.17631451785564423, 0.12828516960144043, -0.00777781568467617, -0.2833285927772522, -0.215087428689003, 0.13726963102817535, -0.6917622089385986, -0.43126380443573, 0.7768541574478149, 0.011556874960660934, -0.16408851742744446, -0.40605682134628296, 0.2665540874004364, 0.2631976008415222, 0.032437872141599655, 0.5387354493141174, -0.0038437971379607916, 0.3707159161567688, 0.5822374224662781, -0.12069375813007355, -0.24845586717128754, 0.10459566116333008, 0.2485947608947754, -0.1968330442905426, -0.2916567921638489, -0.35946381092071533, -0.08520737290382385, -0.0784863606095314, -0.11619977653026581, -0.5832699537277222, 0.6568154692649841, 0.04927215725183487, -0.4870185852050781, -0.2944577634334564, -0.4021395444869995, -0.293192982673645, -0.4929625391960144, -0.0073015121743083, 0.12595070898532867, 0.45363742113113403, -0.10649571567773819, 0.13217681646347046, -0.47094568610191345, -0.24543869495391846, 0.3990762233734131, -0.1973593831062317, 0.47598180174827576, -0.22203528881072998, -0.10378080606460571, 0.27506276965141296, 0.23557516932487488, -0.5706583857536316, -0.5731542110443115, 0.3605639636516571, -0.0936465933918953, 0.33328473567962646, 0.14655859768390656, -0.2266024947166443, 0.011015096679329872, -0.012806910090148449, 0.2079070657491684, 0.28975552320480347, -0.09431169927120209, -1.784651279449463, 0.46575143933296204, -0.15347297489643097, 0.692945659160614, 0.31094688177108765, -0.45426124334335327, -0.08356210589408875, 0.7066530585289001, -0.03810596466064453, 0.15334008634090424, -0.7277652025222778, 0.32292431592941284, -0.4437020719051361, 0.41831329464912415, 0.05171867832541466, -0.4880104660987854, 0.21043425798416138, -0.040033068507909775, -0.2189623862504959, 0.2244897037744522, 0.08317876607179642, 0.2839389145374298, 0.6773902177810669, 0.04592688009142876, 0.024238092824816704, -0.4600253701210022, 0.12852893769741058, 0.7802181243896484, 0.053536541759967804, 0.8300794363021851, 0.2116154134273529, 0.01705331727862358, -0.4620549976825714, -0.0872541218996048, 0.3914189338684082, 0.5398412346839905, 0.04123685136437416, -0.33138734102249146, 0.07718904316425323, 0.2899066209793091, 0.0010421187616884708, 0.0961383655667305, 0.5134011507034302, 0.2330559492111206, 0.5467134118080139, 0.4934159815311432, 0.016544105485081673, 0.21781395375728607, 0.7019643187522888, -0.14420850574970245, -0.4385390281677246, -0.004838862922042608, -0.3665577173233032, -0.5810717940330505, 0.4090862572193146, -0.12639929354190826, -0.0052309283055365086, -0.26974600553512573, -0.5011176466941833, -0.12902924418449402, 0.13558058440685272, -0.376340389251709, -0.46827253699302673, -0.45747965574264526, -0.19339048862457275, -0.6430175304412842, 0.03747249394655228, -0.23190662264823914, 0.10401511937379837, 0.5185085535049438, 0.7965155243873596, 0.02865435555577278, -0.3377552330493927, 0.24657681584358215, -0.19007425010204315, 0.6481647491455078, 0.048383839428424835, 0.0052057718858122826, 0.20676898956298828, -0.2635916769504547, -0.5117331743240356, -0.5263766646385193, -0.6167066693305969, 0.6244660019874573, -0.08384024351835251, 0.22493763267993927, -0.25549477338790894, 0.11429987847805023, 0.29974234104156494, -0.030336905270814896, -0.44233444333076477, 0.24782070517539978, 0.027433784678578377, -0.17857781052589417, -0.5562160611152649, -0.06360022723674774, 0.2955338954925537, -0.05344688147306442, -0.21807809174060822, 0.19278821349143982, -0.39138931035995483, -0.07869333773851395, 0.36843469738960266, 0.32555341720581055, 0.22211110591888428, 0.28292399644851685, 0.5409233570098877, 0.15399135649204254, -0.24175839126110077, -0.4533051550388336, 0.6270595788955688, -0.583636462688446, -0.33055803179740906, -0.37989330291748047, -0.1283114105463028, -0.038592495024204254, 0.7897335290908813, -0.05510080233216286, 2.0844104290008545, -0.02701699361205101, -0.16829532384872437, -0.29319459199905396, 0.5005263090133667, 0.1442207247018814, 0.28583824634552, -0.03944553807377815, -0.3058829605579376, 0.4842221140861511, -0.003521242178976536, 0.6117424964904785, -0.19604647159576416, -0.08113356679677963, 0.40488243103027344, 0.3965385854244232, 0.22634051740169525, 0.04329406097531319, -0.032984428107738495, 0.03240966796875, -0.2881886065006256, -0.11644650250673294, 0.5146275162696838, -0.17425504326820374, 0.28484204411506653, 0.22587409615516663, 0.19605275988578796, 0.09341631829738617, 0.511049747467041, 0.5579445958137512, -0.2601267397403717, -0.14484597742557526, 0.7334237694740295, 0.16425921022891998, -0.3041689991950989, 0.2568339705467224, 0.2875753939151764, -0.1050724983215332, 0.13467419147491455, -0.12288632243871689, -0.2718849778175354, -0.4409138262271881, 0.37630170583724976, 0.10106653720140457, 0.04088607057929039, 0.29861003160476685, -0.4140106439590454, -0.0008262859773822129, 1.0060940980911255, 0.06016876921057701, -0.1575651913881302, -0.08688998967409134, -0.09426338225603104, 0.10685968399047852, 0.7913066148757935, -0.11518444865942001, -0.43794286251068115, -0.12371735274791718, 0.21597135066986084, 0.023030854761600494, -0.22115838527679443, -0.10847141593694687, -0.006550217047333717, -0.13539069890975952, -0.13339769840240479, 0.3471289873123169, 0.13572023808956146, 0.02956848405301571, 0.05527787283062935, -0.10966673493385315, -0.03311416134238243, 0.47504013776779175, -0.04475238174200058, -0.08636077493429184, 0.261067271232605, 0.379972368478775, 0.5026010870933533, -0.3869740962982178, -0.18009109795093536, -2.3513340950012207, 0.4424895644187927, 0.0948239266872406, -0.48021501302719116, 0.2666374146938324, 0.22163604199886322, 0.4379173219203949, -0.028748158365488052, -0.033209364861249924, -0.24955624341964722, -0.0007038700859993696, 0.2514258027076721, -0.12867246568202972, -0.3747367560863495, 0.32468488812446594, -0.296080619096756, -0.0023139130789786577, -0.5538225173950195, -0.48637655377388, -0.9338446855545044, 0.1208425760269165, 0.21136163175106049, 0.09461631625890732, -0.3904205858707428, -0.22007830440998077, 0.43549421429634094, -0.3518597185611725, -0.08671513199806213, 0.030133938416838646, -0.5693283677101135, -0.23952554166316986, -0.3237137496471405, 0.3092636466026306, -0.36622166633605957, 0.1271202713251114, 0.006376427598297596, -0.546247661113739, 0.008928036317229271, -0.4794006049633026, -0.165786474943161, 0.21164770424365997, 0.5332860946655273, 0.11776608228683472, 0.08749077469110489, 0.3142952024936676, -0.39468371868133545, 0.4906102418899536, 0.00019573366444092244, 0.5664306282997131, -0.011041302233934402, 0.5547152161598206, -0.25060558319091797, 0.5097597241401672, -0.09146621078252792, 0.41953498125076294, 0.35104620456695557, -0.16363580524921417, 0.34444931149482727, 0.1616593450307846, -0.21531613171100616, 0.015575308352708817, 0.09889602661132812, -0.027464020997285843, 0.23111847043037415, 0.17251065373420715, 0.06042739003896713, -0.1886216402053833, -0.27803611755371094, -0.3129812479019165, -0.40990695357322693, -0.2662760019302368, -0.09799585491418839, 0.3570200800895691, 0.02857186645269394, 0.17691688239574432, -0.24842680990695953, 0.6473389863967896, -0.2433600127696991, 0.0436951108276844, -0.3592846691608429, 0.056113842874765396, 0.27052897214889526, -0.056008532643318176, -0.2441844940185547, 0.3511657416820526, -5.665262699127197, 0.11298128962516785, 0.034492697566747665, -0.25203046202659607, -0.15034839510917664, -0.6936597228050232, -0.3411289155483246, 0.1331840604543686, 0.2447630763053894, -0.09376644343137741, 0.5600147843360901, -0.4367866814136505, -0.017707282677292824, -0.36070722341537476, 0.30841943621635437, 0.11537154763936996]</t>
+          <t>['high', 'high', 'high', 'medium', 'high', 'high']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[-0.5, -1.0, 0.0, 0.5, -0.5, -0.5]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[4, 5, 5, 3, 5, 5]</t>
+          <t>[40.0, 25.0, 40.0, 35.0, 35.0, 35.0]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['woman', 'woman', 'woman', 'woman', 'woman', 'woman']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>[40.0, 25.0, 40.0, 35.0, 35.0, 35.0]</t>
+          <t>[1, 3, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>['woman', 'woman', 'woman', 'woman', 'woman', 'woman']</t>
+          <t>[4, 5, 5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>[4, 4, 2, 2, 2, 3]</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>[2, 5, 5, 5, 4, 4]</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>[1, 4, 1, 3, 1, 1]</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>[1, 3, 1, 1, 1, 1]</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>[4, 5, 5, 5, 5, 5]</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>[4, 4, 2, 2, 2, 3]</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>[2, 5, 5, 5, 4, 4]</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>[1, 4, 1, 3, 1, 1]</t>
-        </is>
+      <c r="P2" t="n">
+        <v>6</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[1, 3, 1, 1, 1, 1]</t>
+          <t>[4, 4, 2, 2, 1, 2]</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>[4, 4, 2, 2, 1, 2]</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
           <t>[0.16666667 0.5        0.         0.33333333 0.        ]</t>
         </is>
       </c>
-      <c r="T2" t="n">
+      <c r="S2" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -639,85 +627,78 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[4, 4, 2, 3, 2, 3]</t>
+          <t>[nan, '{}', '{}', '{}', '{}', '{}']</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[nan, '{}', '{}', '{}', '{}', '{}']</t>
+          <t>['left', 'left', 'right', 'right', 'left', 'left']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[-0.21125884354114532, 0.3873864412307739, -0.10591500997543335, -0.49510112404823303, -0.39583492279052734, -0.17614871263504028, 1.1094934940338135, 0.352042019367218, -0.2196292132139206, 0.07923385500907898, 0.13090214133262634, -0.004023713991045952, -0.5086208581924438, 0.3759450614452362, 0.683006227016449, 0.24985504150390625, -0.26498860120773315, 0.6137298345565796, -0.054206397384405136, 0.14870090782642365, -0.24567461013793945, -0.26228171586990356, 5.483338100020774e-05, -0.3055267035961151, -0.13675040006637573, 0.28118401765823364, 0.11821666359901428, 0.1384943723678589, -0.09906788915395737, 0.22440341114997864, -0.3228144943714142, 0.22735223174095154, -0.6155533194541931, -0.44256946444511414, 0.37209364771842957, 0.2221219837665558, -0.13368570804595947, 0.38885781168937683, 0.41832396388053894, -0.09401026368141174, -0.323332279920578, 0.04094374552369118, -0.36946338415145874, -0.35311615467071533, -0.16341473162174225, -0.5024817585945129, -3.940455436706543, 0.1649554967880249, -0.36220115423202515, -0.9215824604034424, 0.3655078709125519, -0.5515931248664856, -0.42573416233062744, 0.35368484258651733, -0.5535209774971008, 0.5693815350532532, 0.06854499876499176, -0.12710653245449066, 0.057181451469659805, 0.25359535217285156, 0.17235781252384186, 0.104339599609375, 0.1017574667930603, 0.5013389587402344, -0.0291672945022583, -0.07536215335130692, -0.4778221845626831, 1.0079009532928467, -0.9146602749824524, 0.34735703468322754, -0.7450888752937317, -0.5155202746391296, 0.5811936259269714, -0.05183873325586319, 0.20004476606845856, -0.3078252077102661, -0.07813705503940582, 0.5415634512901306, -0.3451133072376251, 0.5252678394317627, -0.09472861140966415, 0.15391650795936584, -0.22079893946647644, 0.12320276349782944, -0.19480369985103607, 0.6295668482780457, 0.09545701742172241, -0.12174694985151291, 0.18397636711597443, 0.2864932715892792, 0.030456747859716415, -0.4278896152973175, -0.01406465657055378, -0.06906966865062714, 0.3352798521518707, 0.4101865589618683, 0.4041191339492798, 0.24744866788387299, 0.23528586328029633, 0.21968628466129303, 0.4273114800453186, -0.18263240158557892, 0.18868714570999146, -0.5704470276832581, -0.42860525846481323, -0.11795332282781601, -0.10927407443523407, -0.3859090209007263, -0.01572844758629799, -1.7099943161010742, 0.5633503794670105, -0.30344584584236145, -0.1941594034433365, -0.46335673332214355, -0.2012849897146225, 0.5534756183624268, 0.8341748118400574, -0.739448070526123, 0.3143814504146576, 0.45155104994773865, -0.4510174095630646, 0.10017119348049164, 0.4217289686203003, -0.45460423827171326, 0.0562923364341259, 0.24584411084651947, 0.5908433198928833, 0.1610453724861145, 0.7346426248550415, 0.2892630994319916, 0.28166162967681885, 0.586796760559082, 0.03187180683016777, -0.5220937132835388, -0.32132285833358765, 0.0009224824607372284, 0.06757019460201263, -0.08650773018598557, -0.21771936118602753, -0.5156198740005493, -0.49582356214523315, -0.3456652760505676, -2.4797251224517822, 0.30015265941619873, 0.5858224034309387, 0.30679240822792053, -0.5438787341117859, -0.687059760093689, 0.07732435315847397, 0.43892574310302734, 0.10388677567243576, -0.087368905544281, 0.4251614809036255, 0.15153074264526367, -0.5498623251914978, 0.15741735696792603, -0.5309491753578186, -0.4363288879394531, 0.10766762495040894, 0.5097228288650513, -0.001523936982266605, -0.04070230945944786, 0.1476570963859558, 0.3964769244194031, -0.17863984405994415, 0.04273699223995209, 0.09199336916208267, 0.31579795479774475, -0.2195052057504654, -0.44725731015205383, 0.013371480628848076, -0.18418753147125244, 1.2113890647888184, 0.2704527974128723, 0.2911255657672882, -0.5857318639755249, 1.0597840547561646, 0.09735114872455597, -0.0840483233332634, 0.06055837497115135, -0.5722338557243347, 0.09601481258869171, 0.3374719023704529, 0.04082934558391571, 0.5350168943405151, -0.039963118731975555, 1.0022172927856445, 0.06406227499246597, -0.09347838908433914, 0.6315798163414001, -0.7732617259025574, 0.08751064538955688, 0.5550258755683899, 0.5033051371574402, 0.7627608776092529, -0.33633825182914734, 0.5130428671836853, -0.550222635269165, 0.24054624140262604, 0.030077701434493065, -0.1331295520067215, -0.8243975639343262, 0.2967318892478943, -0.08136992901563644, -0.35096579790115356, 4.014882564544678, -0.13617923855781555, -0.025125036016106606, 0.09674732387065887, 0.6193134784698486, -0.4663970470428467, -0.3231520354747772, -0.14402812719345093, -0.4975079596042633, -0.3424013555049896, 0.3042040169239044, 0.9067620038986206, -0.24200096726417542, -0.2547069489955902, 0.3333301544189453, 0.43684715032577515, -0.010374858044087887, -0.3660311698913574, 0.13030846416950226, -0.07627756148576736, -0.0743500217795372, -0.08100827783346176, -0.3187101185321808, -0.11033247411251068, -2.171970844268799, 0.18268081545829773, -0.2554493546485901, 0.1724359393119812, 0.5655346512794495, -0.19738343358039856, 0.5166770219802856, -0.3036684989929199, -0.22453203797340393, -0.09427780658006668, -0.25193873047828674, -0.4642512798309326, 0.6536238193511963, 0.002125623868778348, 0.010744662024080753, -0.1050962507724762, 0.5935257077217102, 0.8993897438049316, -0.7975585460662842, 0.5254186391830444, 0.29340821504592896, 0.1928490549325943, 0.2271631807088852, -0.03857133910059929, -0.38614383339881897, 0.5382639765739441, 0.22852137684822083, 0.1396145075559616, 0.02098257467150688, -0.4968305230140686, -0.34660768508911133, -0.34295719861984253, 0.2835308909416199, 0.14950814843177795, 0.07796168327331543, -0.8536006212234497, 0.28681766986846924, 0.31501495838165283, -0.14494889974594116, -0.6175721883773804, -0.07561266422271729, 0.4523596167564392, 0.022684501484036446, -0.0014741673367097974, -2.288633346557617, 0.08967548608779907, 0.5071180462837219, 0.1317947953939438, 0.3785456717014313, -0.24094414710998535, -0.15232183039188385, -0.02714705467224121, 0.6904794573783875, -1.1198973655700684, 0.2861855924129486, 0.09748189151287079, 0.22777271270751953, 0.07579760253429413, -0.43137723207473755, 0.26280367374420166, -0.3249860405921936, -0.07621291279792786, -0.18028174340724945, -0.15446452796459198, 0.6451237797737122, -0.013823162764310837, -0.1275031566619873, 0.25084182620048523, -0.06465322524309158, -0.10635578632354736, 0.22302885353565216, -0.22209544479846954, -0.20886088907718658, -0.15777543187141418, 0.5049566030502319, -0.2442575842142105, 0.3398545980453491, 0.29132476449012756, -0.6910931468009949, -2.908487558364868, 0.1513819843530655, -0.009152138605713844, -0.6260948777198792, 0.44516927003860474, -0.228395476937294, 0.5125240087509155, -0.08624736964702606, -0.42801633477211, 0.2045246958732605, 0.016181951388716698, -0.5176344513893127, 0.33871155977249146, -0.09752962738275528, 0.3702034652233124, 0.23775072395801544, 0.5394293665885925, -0.24766969680786133, 0.16114801168441772, -0.22535407543182373, 0.13708986341953278, 0.5537582635879517, 0.46552103757858276, -0.2660842835903168, 0.6365756988525391, 0.5650895237922668, -0.5422074794769287, -0.2253655046224594, 0.06756661832332611, 0.29181239008903503, -0.005095140542834997, 0.15714477002620697, 0.2778523564338684, -0.22586199641227722, -0.43058550357818604, -0.22791989147663116, 0.7109541296958923, 0.07912714779376984, 0.5594931840896606, -0.052689943462610245, 0.23127011954784393, 0.38584545254707336, -0.35616764426231384, -0.2224421203136444, 0.5482478737831116, -0.0362299419939518, -0.11198200285434723, -0.36789971590042114, 0.02581310272216797, 0.006033970508724451, -0.40396013855934143, -0.16319862008094788, 0.8699795007705688, 0.39148324728012085, 0.06912574917078018, -0.686301052570343, -0.1639796644449234, 0.38493403792381287, -0.12191465497016907, -0.13438697159290314, 1.072497844696045, -0.1251239776611328, 0.26308366656303406, -0.061306361109018326, 0.18988682329654694, -0.1727786809206009, 0.2469319999217987, -0.8513615727424622, 0.41082698106765747, 0.651781439781189, -0.18743787705898285, 0.3060099184513092, -0.32871007919311523, -1.754679799079895, -0.08500178903341293, 0.1268479973077774, -0.029168011620640755, 0.4008169174194336, -0.19337719678878784, 0.46721169352531433, -0.4410792291164398, -0.079254150390625, -0.6149993538856506, 0.40751343965530396, -0.6288583278656006, -0.2602507770061493, 0.2614765465259552, 0.10643851011991501, -0.6363580822944641, -0.09428302198648453, 0.15125635266304016, 0.4375327527523041, 0.28947874903678894, 0.6679375171661377, -0.5787221193313599, 0.3579327166080475, 0.4743964672088623, -1.09674870967865, 0.3350537419319153, -0.04782792925834656, 0.5762452483177185, -0.31830620765686035, 0.0721026286482811, -0.01903846114873886, -0.09698936343193054, -0.06166106462478638, -0.4213651716709137, 1.1533199548721313, 0.35860782861709595, 0.4018175005912781, -0.6533368825912476, 0.038807693868875504, -0.5266872644424438, 0.3842666447162628, 0.5895688533782959, -0.3318737745285034, -0.18987606465816498, 0.6357356905937195, 0.15082040429115295, 0.34976473450660706, 0.522263765335083, 0.23429609835147858, -0.3230588734149933, -0.495937705039978, -0.7117923498153687, -0.09437722712755203, -0.4241066873073578, -0.35881152749061584, -0.14162705838680267, -0.3558501899242401, 0.4965023398399353, -0.17212344706058502, -0.42067185044288635, -0.2799794673919678, 0.35409173369407654, -0.3456316292285919, -0.03180784359574318, -0.22006234526634216, 0.5266314148902893, 0.07705876976251602, 0.3114147186279297, -0.04367508366703987, -0.09002382308244705, 0.059578679502010345, -0.6153950095176697, 0.750723123550415, -0.5204827189445496, -0.3457958698272705, 0.10262206196784973, 0.8542342782020569, -0.5469550490379333, -0.32544317841529846, -0.11548957228660583, -1.176137089729309, 0.14725945889949799, 0.08948493003845215, -0.404428631067276, -0.3665684461593628, -0.023328645154833794, 0.0075372448191046715, -0.11349441111087799, -0.0914735496044159, -2.1025731563568115, 0.7733333110809326, 0.5951759815216064, 0.12108513712882996, 0.6873926520347595, -0.23330338299274445, -0.5536894202232361, 0.27877169847488403, -0.17169888317584991, -0.20577198266983032, -0.5043649077415466, -0.2291487753391266, -0.1005282998085022, 0.5595203042030334, 0.2905910015106201, 0.03710019960999489, 0.04175100848078728, -0.3017989993095398, -0.2720787227153778, 0.008635221049189568, -0.171005517244339, 0.4035530090332031, 0.6994035243988037, -0.19116896390914917, 0.2189612090587616, -0.3433670997619629, -0.3398846387863159, 0.6621758937835693, -0.2278931438922882, 0.1103542149066925, 0.008073048666119576, -0.16314975917339325, -1.0587114095687866, -0.14943046867847443, 0.35096579790115356, 0.5269619226455688, 0.4278184175491333, 0.41523000597953796, 0.7492819428443909, 0.6990306973457336, -0.09943711757659912, 0.26791641116142273, 0.12570549547672272, 0.23976346850395203, 0.3982456624507904, 0.18916043639183044, -0.04959447309374809, 0.7512801289558411, 0.5683331489562988, -0.9997878670692444, -0.6567490100860596, -0.5473501086235046, 0.17262673377990723, -0.38682693243026733, -0.04478880763053894, -0.18564824759960175, 0.24973297119140625, -0.19886045157909393, -0.6020978689193726, 0.14705634117126465, -0.5718240141868591, 0.2344328761100769, -0.4482423961162567, 0.036808013916015625, -0.9291751980781555, -0.5348473191261292, -0.11970909684896469, -0.5524624586105347, 0.11737512797117233, 0.05391831323504448, 0.40552499890327454, 0.5191378593444824, -0.20448938012123108, 0.3378540277481079, -0.091473788022995, 0.6556528210639954, -0.2204299122095108, -0.050560809671878815, 0.13121475279331207, -0.4224301278591156, 0.3839162588119507, -0.8434243202209473, 0.052382051944732666, 0.6760375499725342, -0.2159755676984787, 0.33218103647232056, 0.03316415846347809, -0.3483675718307495, 0.4160291850566864, -0.4619103968143463, -0.8446126580238342, -0.36392664909362793, -0.09566138684749603, 0.14179684221744537, 0.11272168159484863, -0.3819887638092041, 0.06495022028684616, 0.3547664284706116, 0.16172368824481964, -0.20106655359268188, -0.2541577219963074, -0.009522918611764908, 0.2502920627593994, -0.09644719958305359, 0.6956743001937866, 0.06548827141523361, 0.08212684094905853, 0.05064765736460686, -0.5962313413619995, -0.25817060470581055, 0.3649195432662964, -0.07196459174156189, -0.731868326663971, -0.25882795453071594, 0.015398400835692883, -0.21035191416740417, -0.1890377551317215, -0.13875463604927063, 1.287889003753662, 0.6066777110099792, 0.025516780093312263, -0.4405191242694855, 0.5549365878105164, -0.04259040579199791, 0.052725013345479965, 0.14887304604053497, -0.49027255177497864, 0.6974376440048218, -0.33647093176841736, 0.33873450756073, -1.008508324623108, 0.18365974724292755, 0.8044003248214722, 0.15322305262088776, -0.18597063422203064, -0.2216981053352356, -0.6638882160186768, 0.38122957944869995, 0.08427085727453232, 0.4870474636554718, 0.7882228493690491, -0.3408587574958801, 0.3233746886253357, 0.4749529957771301, 0.022890238091349602, -0.6756587028503418, 0.19286063313484192, 0.7542376518249512, -0.9433748722076416, 0.09898178279399872, 0.3822205364704132, 0.2169404923915863, -0.7871291637420654, 0.3523874580860138, -0.07222610712051392, -0.04534586891531944, -0.332240492105484, 0.15530738234519958, 0.46414098143577576, -0.5281242728233337, 0.7346698641777039, -0.07436840981245041, -0.4534977078437805, 0.5219605565071106, -0.6175304651260376, -0.312715083360672, 0.8132122755050659, 0.45817187428474426, 0.27645668387413025, -0.293760746717453, -0.6709722280502319, -0.08897077292203903, 0.01787392422556877, -0.2942255437374115, -0.039463743567466736, -0.43543168902397156, -0.05921684205532074, -0.039429135620594025, -0.32228702306747437, 0.8163896203041077, -0.3681623637676239, -0.45387977361679077, -0.19792404770851135, 0.2435891479253769, -0.25389203429222107, -0.8631097078323364, 0.21728083491325378, -0.2285049706697464, 0.12304412573575974, 0.5920047760009766, -0.36907342076301575, 0.3016858398914337, 0.4227246046066284, 0.7804798483848572, -0.07372201234102249, -0.33181533217430115, -0.3210548758506775, -2.1725311279296875, 0.4734426438808441, 0.2596258819103241, 0.5121161341667175, 0.0304965041577816, 0.5313918590545654, 0.37933146953582764, 0.040394239127635956, 0.5401599407196045, -0.4481537342071533, 0.7286747694015503, 0.43629199266433716, 0.6158676743507385, -0.08364219218492508, 0.26254868507385254, 0.45344603061676025, 0.4821305274963379, -0.5515859127044678, -0.21682390570640564, -0.8227020502090454, 0.25266432762145996, 0.22155281901359558, -0.1558850109577179, -0.5794478058815002, -0.5557861924171448, 0.2619575560092926, -0.01064428873360157, -0.6010352373123169, 0.14252832531929016, 0.5075100064277649, -0.19666051864624023, 0.3609006404876709, 0.14405232667922974, -0.03945882245898247, 0.07971286028623581, -0.0041956366039812565, -0.48740777373313904, 0.30196911096572876, 0.24411974847316742, -0.22565700113773346, 0.2179737687110901, 0.6135339140892029, 0.17475059628486633, -0.09475145488977432, 0.06354569643735886, -0.3024600148200989, 0.6185099482536316, 0.38872411847114563, 0.7403309941291809, 0.1678246706724167, 0.16833695769309998, -0.2887340486049652, 0.08358090370893478, -0.295322984457016, 0.04323742911219597, 0.6302679777145386, 0.3277529776096344, -0.010371243581175804, -0.3188953995704651, -1.0381511449813843, 0.2349962443113327, 0.23358838260173798, -0.08766718208789825, -0.1317041963338852, 0.6782746315002441, -0.44771650433540344, 0.16268612444400787, 0.5309415459632874, -0.05261524021625519, -0.6085698008537292, -0.3469180464744568, 0.013448294252157211, 0.41638174653053284, 0.304054856300354, -0.39052996039390564, -0.2595655024051666, 0.4874671995639801, 0.11781700700521469, 0.31547439098358154, -0.018231341615319252, -0.2393025904893875, 0.4477918744087219, -0.14312033355236053, 0.2463812530040741, 0.5577985048294067, -5.922809600830078, 0.10762573778629303, -0.5943220257759094, -0.8716166615486145, -0.08273284882307053, -0.8498809933662415, 0.20703645050525665, -0.35524094104766846, 0.012291940860450268, -0.3562879264354706, 0.685897946357727, 0.5103698968887329, -0.27372920513153076, -0.6473087072372437, 0.7380377650260925, 0.36033278703689575]</t>
+          <t>['medium', 'high', 'low', 'high', 'high', 'medium']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[-0.5, -0.5, 0.5, 0.5, -0.5, -0.5]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[3, 5, 2, 4, 4, 3]</t>
+          <t>[30.0, 30.0, 40.0, 35.0, 35.0, 45.0]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['man', 'man', 'man', 'woman', 'woman', 'woman']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[30.0, 30.0, 40.0, 35.0, 35.0, 45.0]</t>
+          <t>[1, 1, 5, 1, 2, 1]</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>['man', 'man', 'man', 'woman', 'woman', 'woman']</t>
+          <t>[3, 3, 2, 3, 3, 4]</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>[1, 1, 5, 1, 2, 1]</t>
+          <t>[5, 4, 3, 2, 3, 2]</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>[3, 3, 2, 3, 3, 4]</t>
+          <t>[5, 3, 5, 5, 4, 4]</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>[5, 4, 3, 2, 3, 2]</t>
+          <t>[1, 1, 4, 1, 2, 1]</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>[5, 3, 5, 5, 4, 4]</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>[1, 1, 4, 1, 2, 1]</t>
-        </is>
+          <t>[1, 1, 1, 1, 1, 1]</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>6</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1, 1]</t>
+          <t>[4, 4, 3, 2, 2, 2]</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>[4, 4, 3, 2, 2, 2]</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
           <t>[0.         0.5        0.16666667 0.33333333 0.        ]</t>
         </is>
       </c>
-      <c r="T3" t="n">
+      <c r="S3" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -737,85 +718,78 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[4, 3, 4, 1, 2, 2]</t>
+          <t>['{}', '{}', '{}', '{}', 'Veteran', '{}']</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['{}', '{}', '{}', '{}', 'Veteran', '{}']</t>
+          <t>['far left', 'center', 'right', 'center', 'far left', 'left']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[-0.04991382732987404, -0.11697617918252945, -0.24798047542572021, -0.6980727314949036, -0.2834433615207672, -0.2023404836654663, 0.7405345439910889, 0.9475526213645935, 0.45176756381988525, -0.2446386069059372, -0.1836933046579361, -0.5459036827087402, -0.14948062598705292, 0.41220399737358093, 0.17922455072402954, -0.06115647032856941, -0.09097663313150406, 0.6787197589874268, 0.012872624211013317, 0.038954656571149826, -0.40093597769737244, -0.16409818828105927, -0.07421860843896866, -0.3503018617630005, -0.09298884123563766, -0.1136506199836731, 0.1787738800048828, -0.45374760031700134, -0.3186515271663666, 0.1421334147453308, 0.02592308633029461, 0.3408053517341614, -0.8704949617385864, -0.5273271799087524, 0.4052237272262573, -0.22549349069595337, -0.22117853164672852, 0.14621447026729584, 0.35500335693359375, -0.03809322044253349, -0.4153597354888916, 0.0111444853246212, 0.1760406345129013, 0.5179303884506226, -0.5243366360664368, -0.3584238290786743, -3.6455748081207275, -0.19174838066101074, -0.4808065891265869, -0.18932980298995972, 0.3349510431289673, -0.09099635481834412, 0.181001678109169, 0.01424111146479845, 0.4524654448032379, 0.6362341642379761, -0.8678861260414124, 0.045241113752126694, -0.3899787366390228, -0.08806424587965012, 0.5081668496131897, -0.03181380033493042, 0.033210404217243195, -0.22715120017528534, 0.1506647765636444, 0.08564307540655136, 0.16971060633659363, 0.8013458251953125, -0.3780878484249115, 0.521991491317749, -0.2446751594543457, -0.20108245313167572, 0.2888883054256439, -0.4242863655090332, -0.08846495300531387, -0.3654056191444397, 0.30172669887542725, 0.6821215748786926, -0.3902186155319214, -0.02291412279009819, -0.42328935861587524, 0.5154210925102234, 0.03600620850920677, 0.3655173182487488, -0.17795053124427795, 0.44238215684890747, -0.6388896703720093, -0.7202295660972595, 0.024742750450968742, 0.7970696687698364, -0.6177248358726501, 0.164067342877388, 0.2919342517852783, 0.74349445104599, 0.7295140624046326, 0.4193477928638458, 0.2913375496864319, -0.053364723920822144, 0.5026987195014954, 0.7451018691062927, 0.5358160734176636, -0.3511170744895935, -0.04545403644442558, -0.8145619034767151, 0.1695365160703659, 0.2660174071788788, -0.18891823291778564, -0.4199831485748291, 0.4623969495296478, -1.9001171588897705, 0.6523410081863403, 0.4700067341327667, -0.37903130054473877, -0.08613255620002747, 0.10713023692369461, 0.8351337313652039, 0.8145265579223633, -0.6824055910110474, 0.4662827253341675, 0.07052363455295563, 0.38983970880508423, 0.20390991866588593, -0.037898704409599304, 0.15989597141742706, 0.1820227950811386, 0.803341269493103, 0.17524151504039764, 0.021026823669672012, 0.4982227087020874, 0.5421289801597595, 0.46381157636642456, 0.9516794085502625, 0.10430409759283066, -1.2371106147766113, -0.3582608699798584, -0.06437601894140244, 0.4897695481777191, -0.1447816640138626, -0.037039633840322495, -0.25806912779808044, -0.6455514430999756, -0.49828532338142395, -2.547569990158081, 0.28495049476623535, 0.8663884997367859, 0.2936011254787445, -0.5476974844932556, -0.1802774965763092, 0.3152584731578827, -0.15267306566238403, 0.0625072717666626, -0.1292513608932495, 0.13775435090065002, -0.4159734547138214, -0.3913719654083252, 0.3620201647281647, -0.8351874351501465, -0.5746190547943115, 0.35695114731788635, 0.7748308181762695, 0.9520968794822693, 0.12269117683172226, -0.09056548029184341, -0.17969658970832825, -0.7167754173278809, -0.056380901485681534, 0.5327596068382263, 0.7755568027496338, -0.33117449283599854, 0.3038257956504822, -0.11055160313844681, -0.100761279463768, 1.1033309698104858, 0.257443904876709, 0.6291577816009521, 0.2395121306180954, 0.06472750008106232, 0.2592855989933014, 0.22529926896095276, 0.3227076530456543, -0.81864333152771, 0.6481292247772217, 0.534367024898529, 0.32646647095680237, 0.6766481399536133, -0.27456966042518616, 0.6765761375427246, -0.4760846495628357, -0.009278771467506886, 0.43844255805015564, -0.1873035728931427, -0.7446960210800171, 0.48022350668907166, -0.040775880217552185, 0.33366164565086365, -0.19870677590370178, 0.5437502861022949, -0.8409932255744934, 0.5311009287834167, 0.5240412354469299, -0.17158882319927216, -0.3030678331851959, 0.2421063631772995, 0.06502425670623779, -0.5623977184295654, 4.032459735870361, 0.27555254101753235, 0.08588074147701263, -0.2605838179588318, 0.2203691601753235, -0.39089101552963257, 0.3030778765678406, -0.11808842420578003, -0.5447540283203125, -0.429051011800766, 0.400786429643631, 0.6419219374656677, -0.594770073890686, -0.12429686635732651, 0.00781512726098299, 0.10114622116088867, 0.08755996078252792, -0.5666813254356384, 0.13641254603862762, -0.5629259347915649, 0.02265557274222374, -0.3297930955886841, 0.22064070403575897, 0.3268170654773712, -2.312988758087158, -0.5281485915184021, 0.25414299964904785, -0.3737247586250305, 0.8431465029716492, -0.1891298145055771, -0.09531674534082413, -0.5333367586135864, -0.5844521522521973, 0.3425431549549103, -0.10180843621492386, 0.12154911458492279, 0.8816617727279663, -0.2078533172607422, 0.0766945406794548, -0.32756736874580383, 0.18928153812885284, 0.32670530676841736, -0.4493674635887146, 0.5508095026016235, -0.1010519489645958, 0.28914228081703186, 0.02031666412949562, -0.2780155539512634, -0.2636054754257202, 0.3302004933357239, 0.03937895596027374, 0.07840584963560104, 0.06257908791303635, -0.3913632333278656, -0.24372544884681702, -0.034555498510599136, 0.36978504061698914, -0.16070741415023804, 0.501487672328949, -0.8963267207145691, -0.5462092757225037, -0.32430189847946167, -0.049390602856874466, -0.18922802805900574, -0.40961605310440063, 0.4983867406845093, -0.007705886382609606, 0.039953190833330154, -2.0456976890563965, 0.6835163831710815, -0.4561758041381836, 0.17398233711719513, 0.28629133105278015, -0.31872186064720154, -0.5021646022796631, 0.2612483501434326, 0.76103276014328, -0.47638311982154846, 0.11645155400037766, 0.5400999784469604, -0.25022366642951965, 0.3542224168777466, 0.18281309306621552, 0.12315976619720459, 0.053274963051080704, -0.23285973072052002, -0.21836480498313904, -0.4614828824996948, -0.42971140146255493, 0.14337356388568878, -0.25202444195747375, 0.18911798298358917, 0.07333831489086151, -0.22794106602668762, 0.2721792459487915, -0.014264932833611965, 0.4016920328140259, 0.054874926805496216, 0.2020428627729416, 0.053115345537662506, -0.40289145708084106, 0.12752319872379303, -0.415214478969574, -3.1013002395629883, -0.011328520253300667, -0.37036749720573425, -0.2678946256637573, -0.05340200662612915, 0.000538838270585984, 0.6122873425483704, -0.3051791191101074, -0.8449732661247253, 0.06363317370414734, 0.13528279960155487, -0.051292404532432556, 0.108904629945755, 0.2835075259208679, 0.5490131974220276, 0.15792903304100037, 0.424579381942749, 0.2671267092227936, 0.691979706287384, 0.017728717997670174, -0.5828071236610413, 0.529174268245697, 0.2513834536075592, -0.06480246782302856, 0.35736986994743347, 0.784552812576294, -0.6589216589927673, -0.20646758377552032, -0.13022081553936005, 0.07205932587385178, 0.03498058021068573, -0.11609068512916565, -0.24861538410186768, -0.15903785824775696, -0.0708397924900055, -0.09524594247341156, 0.4356299340724945, -0.3343936502933502, 0.07721884548664093, -0.22717590630054474, 0.432330459356308, 0.26573607325553894, -0.03451692685484886, 0.7078830599784851, 1.2668007612228394, -0.42905884981155396, 0.07025107741355896, -0.3033945560455322, 0.35618799924850464, -0.46535301208496094, -0.3498171269893646, -0.21108321845531464, 0.8340640068054199, -0.03189210221171379, 0.08382941037416458, -0.43355682492256165, 0.2410525381565094, 0.5308276414871216, -0.005778369028121233, 0.2570978105068207, 1.0373626947402954, 0.16511739790439606, 0.5228838920593262, -0.4091334939002991, 0.21539661288261414, -0.7430893778800964, 0.1329442411661148, -0.8996090292930603, 0.2469685971736908, -0.2271142154932022, 0.17139160633087158, 0.12182074040174484, -0.5150659084320068, -1.513344407081604, 0.06643714010715485, 0.09516812115907669, 0.0058389282785356045, 0.503471851348877, -0.05492868646979332, 0.0735674649477005, 0.03308930993080139, -0.3299618363380432, -0.7148891687393188, 0.2678678631782532, -0.6506621837615967, -0.40844783186912537, -0.14812244474887848, 0.10892008990049362, -0.8450572490692139, 0.1336984634399414, 0.09585615992546082, 0.31414729356765747, -0.05698564648628235, 0.4417871832847595, 0.02050141431391239, 0.02413628064095974, 0.4367130994796753, -0.7731083035469055, 0.26135265827178955, -0.32016721367836, 0.1487991064786911, -0.558445394039154, 0.11842750012874603, -0.42424827814102173, 0.1016797423362732, -0.19192422926425934, -0.4573402404785156, 0.608096718788147, 0.3617064952850342, 0.4185357987880707, -0.0609845332801342, -0.43919262290000916, -0.5007750988006592, 0.10287728905677795, 0.5196139812469482, -0.2901499569416046, -0.13885435461997986, 0.16380135715007782, 0.10683805495500565, 0.5168869495391846, 0.09856561571359634, 1.7257656509173103e-05, 0.015083365142345428, -0.28143084049224854, -0.11387903243303299, 0.0993921160697937, 0.24587349593639374, -0.3363715410232544, -0.3353886902332306, -0.6685740947723389, 0.005032162647694349, -0.2832993268966675, -0.4291056990623474, -0.10562627762556076, -0.18677853047847748, -0.7469993233680725, -0.6634816527366638, -0.10121363401412964, 0.358132541179657, 0.07614254951477051, 0.7875087857246399, 0.09307436645030975, -0.07589414715766907, 0.5249634981155396, -0.40841200947761536, 1.0052815675735474, 0.009475094266235828, 0.4178711175918579, -0.20791330933570862, 0.47375187277793884, -0.5163134932518005, -0.4896015226840973, -0.03675449639558792, -0.9430695176124573, 0.5070257186889648, 0.407670795917511, -0.24895568192005157, -0.03839126229286194, 0.1891886591911316, -0.4719414710998535, 0.25947943329811096, 0.22261008620262146, -1.7519662380218506, 0.9022908210754395, 0.9392262101173401, 0.04683218151330948, 0.08479569852352142, 0.08688818663358688, -0.33309146761894226, 0.4898158609867096, -0.04815341532230377, 0.17857509851455688, -0.5213624238967896, -0.20593665540218353, 0.4689101278781891, 0.10058266669511795, 0.24594737589359283, 0.027891842648386955, -0.18839910626411438, -0.2696966826915741, -0.6096435785293579, 0.26911887526512146, -0.5383389592170715, 0.38793331384658813, 0.5314091444015503, 0.18929235637187958, 0.20647259056568146, -0.2793298065662384, -0.24506773054599762, 0.8836650252342224, -0.1330292522907257, 0.8718317747116089, -0.2886108160018921, -0.44630640745162964, -0.9612748622894287, -0.4255150854587555, 0.44328922033309937, 0.41667911410331726, 0.25759392976760864, -0.1361934095621109, 0.8974518775939941, 0.4349863529205322, -0.1536785066127777, 0.5668132305145264, 0.7216505408287048, -0.19968152046203613, 0.4553474187850952, 0.7806268930435181, -0.29095402359962463, 0.7281468510627747, 0.3830544352531433, -0.6054767370223999, -0.5708698630332947, -0.34970715641975403, -0.6009929180145264, -0.3434341549873352, -0.02090168558061123, -0.006693056784570217, 0.2873891592025757, -0.10045535117387772, -0.8287559151649475, -0.1940852403640747, -0.17997629940509796, -0.12605567276477814, -0.7534093856811523, -0.10394614934921265, -0.15409816801548004, -0.6406883001327515, -0.2171364724636078, -0.81804358959198, -0.1828974485397339, 0.6273002624511719, 1.0467679500579834, 0.4856441020965576, -0.519805908203125, 0.5540037751197815, -0.5446156859397888, 0.2482263594865799, 0.33941882848739624, -0.056034836918115616, 0.5440412163734436, -1.003915786743164, 0.5104947686195374, -0.24305404722690582, -0.2096545696258545, 0.21766716241836548, -0.27441108226776123, 0.5995386838912964, -0.050975341349840164, -0.02526826225221157, 0.020008010789752007, -0.028916558250784874, -0.9905328750610352, -0.4624617397785187, 0.08734801411628723, -0.5506477355957031, 0.09378287196159363, -0.5318541526794434, -0.056494686752557755, -0.30301451683044434, -0.33427441120147705, 0.07558268308639526, -0.08420286327600479, 0.3164641261100769, 0.7247104048728943, 0.14447689056396484, 0.34140780568122864, -0.03360292315483093, 0.3792378008365631, 0.10296542197465897, -0.5723953247070312, -0.36516451835632324, -0.2995757758617401, 0.1728689819574356, -0.43569254875183105, -0.026936382055282593, 0.02963414043188095, -0.8526645302772522, 0.04967385157942772, -0.4081211984157562, 1.5023473501205444, 0.505988597869873, 0.3563695251941681, -0.13439297676086426, 1.0409750938415527, -0.005900267511606216, -0.08325613290071487, 0.2175002098083496, -0.059672992676496506, 0.7317448854446411, -0.44925975799560547, 0.3738365173339844, -0.20604132115840912, 0.129659041762352, 0.7134658694267273, -0.03449633717536926, -0.14581483602523804, -0.7969652414321899, -0.8088573813438416, -0.3170354664325714, -0.3814532160758972, 0.045772653073072433, 0.4342142939567566, 0.22774671018123627, -0.03539289906620979, 0.5438389778137207, -0.06728239357471466, -0.2555328607559204, 0.4617493450641632, 0.7269858717918396, -0.14110715687274933, -0.19044382870197296, -0.23343773186206818, 0.14776711165905, -0.7815033793449402, 0.4160173535346985, 0.027309801429510117, -0.31243446469306946, -0.010567476972937584, 0.05145464465022087, 0.26545774936676025, -0.33802053332328796, 0.6162081360816956, 0.14938919246196747, 0.27251216769218445, 0.7805390954017639, -0.5086045265197754, -0.5210663080215454, 1.2238296270370483, 0.5631835460662842, 0.34943726658821106, 0.21891926229000092, -0.3315277695655823, 0.3039396107196808, 0.3638664782047272, -0.5845072269439697, 0.04650146886706352, -0.11894161254167557, -0.5557177066802979, 0.4850727617740631, -0.18815650045871735, 0.1539643257856369, 0.06561668962240219, -0.10078617185354233, -0.19671764969825745, 0.36953315138816833, -0.25503745675086975, 0.1321978121995926, 0.21080607175827026, -0.24603433907032013, -0.32424604892730713, 0.587256908416748, 0.32108429074287415, 0.08303868025541306, 0.7464088797569275, 0.36289772391319275, -0.14484763145446777, 0.1283065229654312, -0.4660428762435913, -1.7681599855422974, 0.19497531652450562, 0.10555719584226608, -0.2251843512058258, 0.20541274547576904, -0.11303476989269257, 0.18024992942810059, -0.28904569149017334, 0.18758739531040192, 0.05082305520772934, -0.1619410663843155, 0.7836565375328064, 0.0381825752556324, 0.13126611709594727, 0.31029728055000305, 0.30513671040534973, 0.7414482235908508, -0.7720711827278137, -0.5340968370437622, -0.43881386518478394, 0.05171143263578415, 0.369579553604126, -0.13240189850330353, -0.8788856267929077, -0.042193882167339325, 0.4434949457645416, -0.14177489280700684, -0.2917977273464203, 0.171354278922081, 0.1141083762049675, -0.11719055473804474, 0.4238366484642029, -0.12853381037712097, -0.02171195112168789, -0.1190892681479454, -0.8547053933143616, -0.6671991944313049, -0.1834125816822052, 0.34579595923423767, -0.2673852741718292, 0.16617295145988464, 0.8072739839553833, -0.20188239216804504, 0.41337019205093384, 0.1544114351272583, -0.5776562094688416, 0.5431444644927979, -0.5149946212768555, 0.45978206396102905, -0.7168576121330261, 0.42471083998680115, 0.004394293762743473, 0.3227573037147522, -0.5871773958206177, 0.5644943714141846, 0.12539324164390564, 0.10985623300075531, 0.3626032769680023, 0.3601263463497162, -0.33817484974861145, -0.42743533849716187, -0.19229333102703094, -0.7830175757408142, -0.2612302899360657, 0.14323005080223083, -0.21529141068458557, 0.10213927924633026, 0.04843739792704582, 0.10892260074615479, -0.22007378935813904, -0.23170854151248932, -0.6013721227645874, 0.93641597032547, 0.6373735070228577, -0.39745548367500305, -0.040183551609516144, 0.21650150418281555, 0.44338417053222656, 0.4081246852874756, -0.455342561006546, -0.4625840485095978, 0.2514702379703522, -0.5664517879486084, 0.28903689980506897, 0.2805623412132263, -5.278571605682373, -0.29093483090400696, -0.10363281518220901, -0.4694186747074127, -0.18569521605968475, -0.6943098902702332, 0.12015190720558167, -0.4060390889644623, -0.09247457981109619, -0.47452062368392944, 0.3902292251586914, 0.23300902545452118, -0.483874648809433, -0.4174923300743103, 0.5494459271430969, 0.7033321857452393]</t>
+          <t>['high', 'high', 'high', 'high', 'high', 'high']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[-1.0, 0.0, 0.5, 0.0, -1.0, -0.5]</t>
+          <t>['black', 'black', 'hisp', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>[25.0, 35.0, 30.0, 40.0, 35.0, 35.0]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>['woman', 'man', 'man', 'woman', 'man', 'woman']</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>[3, 1, 3, 1, 1, 1]</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>[5, 4, 5, 5, 5, 5]</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>['black', 'black', 'hisp', 'white', 'white', 'white']</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>[25.0, 35.0, 30.0, 40.0, 35.0, 35.0]</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>['woman', 'man', 'man', 'woman', 'man', 'woman']</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>[3, 1, 3, 1, 1, 1]</t>
+          <t>[3, 2, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>[5, 4, 5, 5, 5, 5]</t>
+          <t>[5, 4, 4, 5, 5, 4]</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>[3, 2, 2, 1, 1, 1]</t>
+          <t>[4, 1, 1, 1, 5, 1]</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>[5, 4, 4, 5, 5, 4]</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>[4, 1, 1, 1, 5, 1]</t>
-        </is>
+          <t>[5, 3, 4, 1, 1, 1]</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>6</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>[5, 3, 4, 1, 1, 1]</t>
+          <t>[4, 3, 4, 1, 1, 1]</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>[4, 3, 4, 1, 1, 1]</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
           <t>[0.5        0.         0.16666667 0.33333333 0.        ]</t>
         </is>
       </c>
-      <c r="T4" t="n">
+      <c r="S4" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -835,85 +809,78 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[5, 5, 3, 3, 2, 3]</t>
+          <t>['{}', '{}', 'none', '{}', '{}', '{}']</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['{}', '{}', 'none', '{}', '{}', '{}']</t>
+          <t>['left', 'center', 'left', 'center', 'left', 'far left']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[-0.042324356734752655, 0.20226505398750305, -0.0767546147108078, -0.17247891426086426, -0.257876455783844, 0.11489276587963104, 0.3379886746406555, 0.5127077102661133, -0.17030119895935059, -0.2525446116924286, -0.019011126831173897, 0.23024696111679077, 0.06531087309122086, 0.6742764711380005, 0.008569641970098019, 0.2144356071949005, -0.15133710205554962, 0.1480068415403366, 0.20810198783874512, -0.21547415852546692, 0.11018257588148117, 0.023110877722501755, -0.09308881312608719, -0.42519694566726685, -0.08156809210777283, -0.1247478649020195, -0.37997934222221375, 0.024302443489432335, -0.06331465393304825, 0.39143839478492737, -0.12211984395980835, 0.40945783257484436, 0.07636886090040207, 0.05019781365990639, 0.18083621561527252, -0.3397943079471588, 0.2967706322669983, 0.006330644711852074, -0.06348579376935959, -0.015618718229234219, 0.06379497051239014, 0.12385551631450653, 0.18584834039211273, 0.035661544650793076, 0.025680577382445335, -0.25464630126953125, -2.6458938121795654, -0.32570862770080566, -0.0788639485836029, -0.24704360961914062, 0.3010123372077942, -0.2241487354040146, -0.0438963957130909, -0.00579975638538599, -0.36985108256340027, 0.6158398389816284, 0.08768628537654877, 0.3534407913684845, 0.5964738130569458, 0.46778926253318787, -0.08545812219381332, -0.14215897023677826, 0.0025787868071347475, 0.2580632269382477, -0.20565089583396912, 0.4001050293445587, -0.1431771069765091, 0.8299345374107361, -0.054150696843862534, 0.5006296038627625, -0.40600523352622986, -0.12574061751365662, 0.5280678868293762, 0.13106520473957062, -0.1935485452413559, -0.450600266456604, 0.032275885343551636, 0.06067819148302078, -0.4530543088912964, 0.04864481836557388, 0.23701749742031097, 0.2679486572742462, 0.23236459493637085, 0.19510403275489807, 0.05883558467030525, 0.20798972249031067, -0.1743946224451065, -0.2581214904785156, 0.06327231228351593, 0.4436708688735962, 0.060543373227119446, 0.24095091223716736, -0.020298119634389877, 0.5755447745323181, 0.020482733845710754, -0.0077551016584038734, 0.09250078350305557, 0.09390962868928909, 0.13460268080234528, -0.029213782399892807, -0.007200993597507477, -0.015494531020522118, 0.1660909801721573, -0.29960787296295166, -0.05622651055455208, 0.12055418640375137, 0.0369756817817688, 0.0604596771299839, 0.38583096861839294, -2.3387537002563477, 0.26099684834480286, 0.25196585059165955, 0.2679998278617859, 0.1235070452094078, 0.09362602978944778, 0.3417071998119354, 0.33554041385650635, -0.1842738837003708, -0.07890079915523529, -0.12521924078464508, -0.29733744263648987, -0.013498986139893532, 0.08178269118070602, 0.020667359232902527, 0.3072040379047394, 0.3317916691303253, -0.24931883811950684, -0.3529914915561676, 0.009136758744716644, 0.035962119698524475, 0.21593569219112396, 0.5393639206886292, -0.19005614519119263, -0.4294828474521637, 0.04523637890815735, 0.18539659678936005, 0.4511931538581848, -0.08588773757219315, -0.01851920783519745, -0.05959140881896019, -0.31365668773651123, -0.16634635627269745, -2.8763880729675293, 0.21661804616451263, 0.6137387752532959, 0.0056518372148275375, -0.45506224036216736, 0.2522282004356384, 0.03916795551776886, 0.5438407063484192, -0.258820116519928, 0.2191733568906784, 0.07078883051872253, 0.01916567049920559, -0.3729839026927948, -0.41658180952072144, -0.32612699270248413, -0.14161700010299683, 0.4388384222984314, 0.46323734521865845, -0.11792488396167755, -0.14963607490062714, 0.01234422530978918, -0.3735004663467407, -0.4652550220489502, -0.35750022530555725, -0.14565159380435944, -0.21588623523712158, -0.09638772904872894, -0.4170362055301666, 0.0734173133969307, -0.049133043736219406, 0.5139352083206177, 0.247430220246315, 0.49033549427986145, -0.19165638089179993, 0.36439985036849976, -0.014055822044610977, -0.40643322467803955, -0.11617299914360046, -0.24216166138648987, 0.24544058740139008, 0.2663981318473816, 0.2421494871377945, 0.1737145334482193, 0.05718230828642845, 0.07362205535173416, -0.2739783525466919, 0.27431854605674744, 0.3436930477619171, -0.4179612398147583, -0.07602323591709137, 0.37997615337371826, 0.2664864957332611, 0.5900301337242126, -0.4997464716434479, 0.23998835682868958, -0.7628113031387329, 0.24288834631443024, -0.000915174197871238, 0.4576243460178375, -0.2243531346321106, 0.04630667343735695, 0.2026951014995575, -0.10866980999708176, 4.016849040985107, 0.10791676491498947, -0.12405384331941605, 0.15219299495220184, 0.5222424864768982, 0.06085781753063202, 0.01808575540781021, -0.16140718758106232, -0.22503381967544556, 0.22898195683956146, -0.2648167908191681, 0.47077831625938416, -0.05585798993706703, -0.6317272186279297, 0.15216751396656036, 0.008993574418127537, 0.2528327405452728, 0.04297928139567375, -0.0009651896543800831, -0.07561235129833221, 0.02868831343948841, 0.04637168347835541, -0.2037723958492279, -0.2453809678554535, -1.4713166952133179, -0.026682496070861816, -0.24694107472896576, -0.22617018222808838, 0.47510504722595215, -0.14722806215286255, 0.23210172355175018, 0.14113016426563263, -0.37538838386535645, 0.017620783299207687, -0.10151412338018417, -0.2987312972545624, -0.04059237986803055, 0.4011671245098114, 0.2335626780986786, -0.30041542649269104, 0.37295934557914734, 0.17254918813705444, -0.5572916269302368, 0.27381736040115356, 0.35407379269599915, 0.6750142574310303, -0.08603159338235855, 0.212820902466774, -0.5221492052078247, -0.38568833470344543, -0.11746475845575333, -0.05259617045521736, -0.032205112278461456, -0.06192941591143608, -0.1442161202430725, -0.33590149879455566, 0.018088584765791893, -0.05732152983546257, -0.24413543939590454, -0.03640894964337349, -0.08706577867269516, -0.45018476247787476, -0.4053809940814972, 0.08339012414216995, 0.08538033068180084, 0.46510931849479675, 0.38180482387542725, -0.6365898251533508, -3.5717077255249023, -0.15373079478740692, 0.2989566922187805, 0.4325045049190521, 0.4092884063720703, -0.42913103103637695, -0.0025469670072197914, 0.26009896397590637, 0.4495743215084076, -0.4829584062099457, 0.5661299824714661, 0.011942800134420395, 0.08340702950954437, 0.06503493338823318, -0.29065439105033875, 0.028945796191692352, 0.14722394943237305, 0.028462959453463554, 0.01725614257156849, 0.12343187630176544, 0.2323860377073288, 0.10988147556781769, -0.2451503574848175, -0.35274407267570496, 0.22728075087070465, -0.007816770114004612, -0.5637004375457764, -0.10101447999477386, 0.15811285376548767, -0.13448572158813477, 0.1825105845928192, -0.19951310753822327, -0.013301531784236431, -0.014453770592808723, -0.002877909457311034, -3.7034201622009277, 0.11413295567035675, -0.3361791670322418, -0.5448142290115356, 0.526451587677002, -0.37513676285743713, 0.3869134783744812, -0.045272279530763626, -0.311751127243042, -0.08662696182727814, 0.023194998502731323, 0.10768414288759232, 0.3899848461151123, 0.01335829496383667, 0.5443126559257507, -0.33052584528923035, -0.1143769696354866, -0.0074876160360872746, -0.10592903196811676, 0.04460390284657478, 0.10272926092147827, 0.10633305460214615, -0.13322950899600983, -0.02562166564166546, -0.025467295199632645, 0.400422066450119, -0.18300418555736542, 0.03457050770521164, -0.24437136948108673, 0.1448163092136383, -0.19258926808834076, -0.022480318322777748, 0.22007133066654205, 0.07737129181623459, -0.12516248226165771, -0.3796522319316864, 0.02619975619018078, 0.3607206642627716, 0.579038143157959, 0.4588279724121094, 0.2534210681915283, 0.16152040660381317, -0.26597511768341064, 0.021200791001319885, 0.38991042971611023, 0.14593085646629333, -0.16583478450775146, -0.6578190326690674, 0.07423968613147736, 0.11549855023622513, -0.05076845735311508, -0.12294013053178787, 0.804487943649292, -0.29566794633865356, 0.056836050003767014, -0.226548969745636, 0.08661160618066788, 0.2843974530696869, -0.12570078670978546, -0.255810409784317, 1.1366016864776611, -0.283904105424881, 0.035012099891901016, -0.009883243590593338, -0.19599288702011108, -0.08575929701328278, 0.4519539177417755, -0.4964498281478882, 0.3156166076660156, 0.3822987675666809, -0.36231645941734314, 0.28455203771591187, 0.047249242663383484, -1.1641823053359985, 0.12289096415042877, 0.6162489652633667, -0.17048905789852142, 0.4878993630409241, 0.02472197636961937, -0.10166162997484207, -0.1612437516450882, 0.19363094866275787, -0.037397563457489014, 0.5745453834533691, -0.4510428011417389, -0.4131738245487213, -0.18132178485393524, 0.07210090756416321, -0.4666909873485565, 0.29943475127220154, -0.286856085062027, 0.5058500170707703, 0.4077991843223572, 0.08511540293693542, 0.5829561352729797, 0.24025559425354004, 0.057238418608903885, -0.8510854244232178, 0.11906363815069199, -0.19707581400871277, 0.009903051890432835, -0.49083930253982544, -0.2099841833114624, -0.029001131653785706, -0.18610674142837524, -0.29389676451683044, -0.26868513226509094, 0.6467573046684265, -0.18698808550834656, 0.5220430493354797, -0.06881823390722275, -0.005021550226956606, 0.5212974548339844, 0.41973406076431274, 0.6206457614898682, -0.1097177043557167, -0.06260456889867783, 0.5000080466270447, -0.27554675936698914, -0.07965187728404999, 0.1805853545665741, 0.13923797011375427, -0.09026412665843964, 0.05191081017255783, -0.31664642691612244, -0.04610322043299675, 0.12054441124200821, -0.42615747451782227, -0.2996942102909088, -0.16268767416477203, 0.14495021104812622, -0.35192808508872986, -0.07060044258832932, -0.7618241906166077, -0.14592890441417694, -0.483320027589798, -0.31782448291778564, 0.1197187528014183, 0.4234943091869354, 0.027946826070547104, 0.22027337551116943, -0.38088974356651306, 0.1603969782590866, 0.3456616699695587, -0.3870387673377991, 0.7255929708480835, -0.1820208728313446, -0.005649144295603037, -0.05262010172009468, 0.20494344830513, -0.3801472783088684, -0.0881069004535675, 0.21535724401474, -0.21758222579956055, -0.056316182017326355, -0.12309379130601883, -0.4914087951183319, -0.2544851303100586, 0.0716458112001419, 0.10313989967107773, -0.11539392173290253, 0.026567626744508743, -1.4810432195663452, 0.6910890340805054, -0.03389206528663635, -0.19907592236995697, 0.619543731212616, -0.26373666524887085, -0.10856808722019196, 0.5088029503822327, -0.30106085538864136, 0.27158331871032715, 0.08980894833803177, 0.012461716309189796, -0.009316856972873211, 0.10394836962223053, -0.33799365162849426, -0.0032668965868651867, 0.15650983154773712, -0.1749989092350006, 0.04083503037691116, 0.04292178526520729, -0.19991782307624817, 0.3807634115219116, 0.3084445893764496, -0.0280415341258049, -0.28016266226768494, 0.16489292681217194, 0.2054552584886551, 0.737336277961731, -0.1770409792661667, -0.12361767143011093, -0.2926860749721527, -0.11297248303890228, -0.5245440006256104, 0.16284222900867462, 0.09961659461259842, 0.32968994975090027, 0.31242886185646057, -0.19749201834201813, 0.33090344071388245, 0.18759699165821075, -0.2734360694885254, 0.1747790277004242, 0.04811045899987221, 0.06474529951810837, 0.427633136510849, 0.24262066185474396, -0.03302769362926483, 0.19814848899841309, 0.22259844839572906, -0.5903553366661072, -0.4528399109840393, -0.23759661614894867, -0.12282837927341461, -0.0956190973520279, 0.26789721846580505, -0.025692271068692207, 0.1791759580373764, -0.33817461133003235, -0.08628877252340317, -0.2340766340494156, -0.37920066714286804, 0.01617235317826271, -0.276325523853302, 0.259055495262146, -0.5696515440940857, -0.45607104897499084, 0.22259917855262756, -0.2817542254924774, -0.11249736696481705, 0.3304610848426819, 0.36001068353652954, 0.3263663947582245, -0.06733590364456177, 0.08199736475944519, -0.12960435450077057, 0.4539380371570587, -0.002580575877800584, 0.11692805588245392, 0.4222906231880188, -0.12980015575885773, 0.06048963963985443, -0.5623773336410522, -0.3985055387020111, 0.4731198251247406, -0.1498827189207077, 0.2133699208498001, 0.48692676424980164, 0.11371827125549316, 0.369027316570282, -0.306706964969635, 0.12429375946521759, -0.471414178609848, -0.06375303119421005, 0.419472336769104, -0.49283623695373535, 0.04834230989217758, 0.0014220605371519923, -0.09143150597810745, -0.22414211928844452, 0.08123970776796341, -0.18908578157424927, 0.11118549108505249, 0.1222064271569252, 0.2683667838573456, -0.0077569750137627125, 0.5500673651695251, 0.5045959949493408, 0.046791110187768936, -0.3387180268764496, -0.3092096447944641, 0.1473696529865265, 0.10065849125385284, -0.4238416850566864, 0.08542635291814804, -0.16736595332622528, 0.08896178752183914, 0.3469470739364624, -0.1501285582780838, 1.7693182229995728, 0.3586237132549286, 0.25901344418525696, -0.014481082558631897, 0.5424442887306213, 0.3173229396343231, -0.024173473939299583, -0.10425903648138046, -0.5843430161476135, 0.43776753544807434, 0.23784269392490387, 0.6360827088356018, -0.11153283715248108, 0.1007235199213028, 0.24984151124954224, 0.24665135145187378, 0.16406308114528656, -0.3205743134021759, -0.23560035228729248, 0.44330188632011414, -0.46012917160987854, 0.09380659461021423, 0.3760640621185303, -0.2598711848258972, 0.2582213580608368, 0.3752427101135254, 0.1851988583803177, -0.25402379035949707, 0.2100391983985901, 0.11721045523881912, 0.21681608259677887, -0.09876647591590881, 0.2965042293071747, 0.4343053102493286, -0.20561198890209198, 0.06773249804973602, 0.2526530921459198, -0.2384093552827835, -0.5050866603851318, 0.06825633347034454, 0.27818921208381653, -0.10351008921861649, 0.7293427586555481, -0.054252661764621735, 0.15224775671958923, 0.5898187160491943, -0.25773265957832336, -0.02190553955733776, 0.6190860867500305, 0.5864144563674927, -0.22416187822818756, -0.11301354318857193, -0.11748712509870529, -0.10023432224988937, -0.18751955032348633, -0.21288469433784485, 0.07102322578430176, -0.5898897647857666, -0.3164600431919098, 0.18805308640003204, -0.10588964819908142, 0.10681740939617157, 0.20339396595954895, -0.26666706800460815, -0.11588790267705917, 0.08874616771936417, -0.06564744561910629, -0.06045052036643028, 0.23491454124450684, -0.22212056815624237, -0.3141257166862488, 0.20156869292259216, 0.023081963881850243, -0.3304263949394226, 0.5677853226661682, 0.40306445956230164, 0.18090938031673431, -0.11976028978824615, -0.5731770992279053, -2.8984999656677246, 0.09772897511720657, -0.06055719777941704, -0.126546710729599, -0.3652116656303406, 0.38152015209198, -0.03708857670426369, -0.03000853769481182, -0.186759352684021, -0.21855764091014862, -0.07978420704603195, 0.4789413511753082, 0.2904399037361145, -0.29467394948005676, 0.1863454133272171, 0.33574897050857544, 0.15699836611747742, -0.25070104002952576, -0.22378009557724, -0.007595862727612257, 0.22793585062026978, 0.18377578258514404, -0.5519630908966064, -0.32151973247528076, 0.04429533705115318, 0.3728688359260559, 0.16369032859802246, -0.18264245986938477, 0.23876512050628662, 0.5199028849601746, -0.09647296369075775, 0.16412827372550964, 0.008380096405744553, 0.08064231276512146, -0.17611348628997803, 0.04012082889676094, 0.03002927079796791, 0.09512372314929962, -0.08989613503217697, -0.27128422260284424, 0.2809883952140808, 0.39218610525131226, 0.23695942759513855, -0.07369963079690933, 0.25748685002326965, -0.2119862139225006, 0.21927712857723236, -0.2842172086238861, 0.45762899518013, -0.3681534230709076, 0.5859132409095764, -0.21627137064933777, 0.4487372934818268, -0.2162507027387619, 0.4487573206424713, 0.3193225562572479, -0.022252732887864113, 0.1443709284067154, -0.14916940033435822, -0.3133186995983124, -0.18662916123867035, 0.10636407136917114, -0.09812136739492416, 0.12260992079973221, 0.3224540650844574, -0.4028746783733368, -0.37944266200065613, -0.5879324078559875, -0.07917514443397522, 0.17947207391262054, -0.2575404644012451, -0.3977232277393341, 0.20235468447208405, 0.4249454438686371, -0.12719962000846863, 0.29031485319137573, 0.4441220462322235, -0.021403681486845016, 0.09953657537698746, 0.029403081163764, 0.035184115171432495, -0.3674796521663666, -0.5252752900123596, 0.06082881987094879, 0.15589629113674164, -6.986705303192139, -0.11844036728143692, 0.024139320477843285, -0.2765195667743683, -0.05269898846745491, -0.34438732266426086, 0.017959387972950935, -0.3126457631587982, -0.2679870128631592, 0.11633460968732834, 0.4654429852962494, -0.04589465260505676, -0.45420002937316895, -0.17677025496959686, 0.5243886709213257, 0.2863847315311432]</t>
+          <t>['high', 'high', 'low', 'low', 'low', 'high']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[-0.5, 0.0, -0.5, 0.0, -0.5, -1.0]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[4, 5, 2, 2, 2, 4]</t>
+          <t>[40.0, 45.0, 50.0, 35.0, 40.0, 25.0]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['woman', 'man', 'man', 'man', 'man', 'man']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>[40.0, 45.0, 50.0, 35.0, 40.0, 25.0]</t>
+          <t>[1, 1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>['woman', 'man', 'man', 'man', 'man', 'man']</t>
+          <t>[4, 5, 2, 2, 4, 4]</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 3, 1, 1]</t>
+          <t>[4, 5, 2, 2, 3, 3]</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>[4, 5, 2, 2, 4, 4]</t>
+          <t>[2, 4, 5, 3, 5, 5]</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>[4, 5, 2, 2, 3, 3]</t>
+          <t>[1, 1, 3, 1, 1, 1]</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>[2, 4, 5, 3, 5, 5]</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>[1, 1, 3, 1, 1, 1]</t>
-        </is>
+          <t>[1, 5, 1, 1, 1, 1]</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>6</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>[1, 5, 1, 1, 1, 1]</t>
+          <t>[5, 5, 3, 2, 2, 3]</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>[5, 5, 3, 2, 2, 3]</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
           <t>[0.         0.33333333 0.33333333 0.         0.33333333]</t>
         </is>
       </c>
-      <c r="T5" t="n">
+      <c r="S5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -933,85 +900,78 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[5, 4, 4, 5, 5, 5]</t>
+          <t>['Black american', '{}', '{}', '{}', '{}', '{}']</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['Black american', '{}', '{}', '{}', '{}', '{}']</t>
+          <t>['left', 'left', 'center', 'right', 'far left', 'far left']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[-0.12828494608402252, 0.061020202934741974, 0.373921275138855, -0.12586140632629395, -0.4833848476409912, -0.6852855086326599, 0.7627004384994507, 1.0769171714782715, 0.5861382484436035, -0.6518661975860596, 0.3606930375099182, -0.2406730055809021, 0.06546232849359512, 0.2544763386249542, 0.43260541558265686, 0.4685973525047302, 0.1409703940153122, 0.5691900253295898, 0.007278991863131523, 0.31257060170173645, -0.027645902708172798, -0.7561770081520081, 0.14410400390625, -0.1754257082939148, 0.4931351840496063, -0.14603860676288605, 0.04795387387275696, -0.40755495429039, -0.23116612434387207, 0.02712891437113285, -0.10054271668195724, 0.2879422605037689, -1.0614516735076904, -0.23491913080215454, 0.8637434840202332, 0.16608022153377533, 0.42719781398773193, 0.3432461619377136, 0.6672414541244507, 0.2824654281139374, 0.00620165653526783, -0.028995346277952194, -0.10970135033130646, -0.17145588994026184, -0.2614622116088867, -0.08092692494392395, -4.3185133934021, 0.0005540998536162078, 0.21754825115203857, -0.38243570923805237, 0.6293250322341919, -0.628614068031311, -0.22502723336219788, 0.37103912234306335, 0.17637011408805847, 0.1986510455608368, -1.1479442119598389, 0.08316174149513245, -0.5399889945983887, -0.32902368903160095, 0.4131946563720703, 0.26448020339012146, -0.2615227997303009, 0.27054956555366516, 0.0944114699959755, 0.4973055422306061, -0.3346700966358185, 0.7276750802993774, -0.5462067723274231, 0.7844893336296082, -0.119001604616642, -0.48789921402931213, 0.3716594874858856, 0.07255362719297409, -0.047424644231796265, -0.024479739367961884, -0.07922002673149109, 0.4066486358642578, -0.7822210192680359, 0.2602398693561554, -0.43099498748779297, 0.28502577543258667, -0.25839963555336, 0.3839871287345886, -0.28904739022254944, 0.34491485357284546, -0.0667203739285469, -0.4637492001056671, 0.4753088057041168, -0.0546073317527771, -0.6879211664199829, -0.12213412672281265, -0.49453699588775635, -0.005162600893527269, 0.8295483589172363, -0.05225273594260216, 0.5217787623405457, 0.30650344491004944, 0.3603087067604065, 0.4835902452468872, 0.5993161201477051, -0.15548072755336761, 0.006357102654874325, -0.7859573364257812, -0.8483091592788696, 0.14943791925907135, 0.0007023126818239689, 0.1763172149658203, 0.1154593750834465, -1.586446762084961, 0.24589717388153076, -0.09113699942827225, -0.33476343750953674, -0.6930838227272034, -0.46933308243751526, 0.20103834569454193, 0.5054545998573303, -0.6669913530349731, 0.22263942658901215, -0.3235864043235779, -0.14256249368190765, 0.24603067338466644, -0.07989523559808731, 0.0899820551276207, 0.16670145094394684, 0.3949924409389496, -0.07586270570755005, 0.21440042555332184, 0.7719742059707642, 0.5386198163032532, 0.5240209102630615, 0.6825310587882996, -0.157659649848938, -0.8104084730148315, -0.30972951650619507, 0.0007983144023455679, -0.04795502498745918, -0.330270379781723, -0.5083584189414978, -0.3453800678253174, -0.5809561610221863, -0.5495616793632507, -2.635711431503296, 0.4598984718322754, 0.7377892136573792, 0.04797673225402832, -0.7358707189559937, 0.12746450304985046, -0.4996351897716522, -0.0950080007314682, -0.06633411347866058, 0.14249956607818604, -0.14546246826648712, -0.07203726470470428, -0.7107775211334229, 0.12769566476345062, -0.2737880349159241, -0.6746453046798706, 0.05629797279834747, 1.1177408695220947, 0.21505896747112274, 0.13979601860046387, -0.02115735597908497, 0.34002748131752014, -0.13765791058540344, 0.3404552936553955, 0.12329510599374771, 0.5984309911727905, 0.4105646312236786, -0.25140225887298584, 0.3501589298248291, -0.035779792815446854, 0.7544286251068115, 0.14853622019290924, 0.4187582731246948, -0.1793038249015808, 1.0323597192764282, 0.6207836866378784, 0.2218884825706482, -0.16436389088630676, -0.7982653379440308, 0.6114651560783386, 0.2467890828847885, -0.2491699904203415, 0.8120760917663574, -0.36150938272476196, 0.5859275460243225, 0.2811345160007477, -0.2319267839193344, 0.07552768290042877, -0.5871101021766663, -0.7969119548797607, 0.4170518219470978, 0.3261602520942688, 0.6068849563598633, -0.223387211561203, 1.0195012092590332, -0.3898830711841583, -0.06826015561819077, 0.20762547850608826, 0.28000080585479736, -0.06416316330432892, 0.7403615713119507, 0.2580379247665405, -0.7712695598602295, 3.966416358947754, -0.2844076156616211, -0.08138687908649445, 0.19815418124198914, 0.31707367300987244, -0.6479791402816772, -0.22850915789604187, -0.035764556378126144, -0.14981608092784882, -0.6320686936378479, 0.2089553028345108, 0.6894409656524658, -0.8108624219894409, -0.14552971720695496, -0.13327987492084503, 0.39061444997787476, 0.11920166015625, -0.17041397094726562, 0.0543377660214901, -0.5540298223495483, -0.27181288599967957, 0.0185826625674963, -0.28615397214889526, 0.351546972990036, -2.478433847427368, -0.2816496193408966, -0.21954552829265594, -0.1679031252861023, 0.5781890749931335, -0.3061929941177368, 0.07121821492910385, 0.4140835702419281, -0.3796609938144684, 0.22384214401245117, -0.09314511716365814, -0.04510887339711189, 0.08599578589200974, -0.31743085384368896, 0.16948677599430084, -0.7610617280006409, 0.39163875579833984, 0.6670601963996887, -0.686407208442688, 1.0911860466003418, 0.21443982422351837, 0.3760029077529907, 0.5940991640090942, 0.38358718156814575, -0.7213887572288513, 0.8077062368392944, 0.16606053709983826, -0.2702876329421997, -0.3171194791793823, -0.8467023968696594, -0.6013867259025574, -0.3346961438655853, 0.609279990196228, -0.7938557267189026, 0.48741310834884644, -1.1597577333450317, -0.5824143886566162, 0.21257299184799194, 0.06513449549674988, -0.2557011544704437, -0.28452616930007935, 0.3013458251953125, 0.2660661041736603, 0.07676396518945694, -2.025800943374634, -0.04083731025457382, -0.38005974888801575, 0.13277266919612885, 0.16285237669944763, -0.2564721703529358, -0.8883259892463684, -0.2289920449256897, 0.2535145878791809, -0.5329846739768982, 0.5655747056007385, 0.0693807303905487, 0.18947458267211914, 0.376645565032959, -0.6418182849884033, 0.045666322112083435, 0.0878862589597702, -0.4088912904262543, -0.6734281182289124, -0.40882188081741333, -0.2719210684299469, 0.09871926158666611, 0.146299347281456, 0.4509752094745636, 0.18682248890399933, -0.25525331497192383, 0.2043340653181076, -0.43004128336906433, 0.08642071485519409, 0.12202194333076477, 0.5971786975860596, -0.26868394017219543, -0.014043056406080723, 0.07183218002319336, -0.5100592374801636, -2.8346407413482666, -0.1425936371088028, 0.0814286544919014, 0.04017891734838486, 0.10773193836212158, 0.18860164284706116, 1.2155022621154785, -0.39527925848960876, -0.272121399641037, -0.4318903982639313, 0.12681211531162262, 0.31025466322898865, -0.08688202500343323, -0.13425065577030182, 0.35400280356407166, 0.10945714265108109, 0.7348437905311584, -0.16628344357013702, 0.8251518607139587, 0.07609298080205917, -0.033442314714193344, 0.1615389585494995, 0.4614335298538208, -0.16229155659675598, 0.8245216608047485, 0.43350616097450256, -0.9433388113975525, -0.010920978151261806, 0.2408006340265274, 0.014118135906755924, 0.5871210098266602, -0.020884301513433456, 0.4650813639163971, -0.21629413962364197, -0.13969868421554565, -0.7588161826133728, 0.3714776337146759, -0.5679957866668701, 0.28326931595802307, -0.23940669000148773, 0.35659199953079224, 0.042441848665475845, 0.14211083948612213, 0.04545829817652702, 0.6013321280479431, 0.1581297665834427, 0.12216481566429138, -0.31375953555107117, 0.14097218215465546, 0.48617273569107056, -0.32358312606811523, -0.16307660937309265, 1.3497415781021118, 0.14596448838710785, 0.18602988123893738, -0.06908972561359406, 0.02506262995302677, 0.5453253388404846, 0.13727916777133942, 0.09004314243793488, 0.9747626781463623, 0.09864521771669388, -0.17326408624649048, 0.10064804553985596, -0.5241292119026184, -0.397378146648407, 0.401274174451828, -0.5269978046417236, -0.14456531405448914, 0.46102380752563477, 0.017158573493361473, 0.11357775330543518, -0.4933708608150482, -1.6601998805999756, 0.1189093217253685, 0.03316991403698921, -0.14314201474189758, 0.3694700002670288, 0.019956106320023537, 0.17957057058811188, -0.006651304196566343, -0.24924734234809875, -0.3879125118255615, 0.4653449058532715, -0.3515031635761261, 0.03488123416900635, -0.14773522317409515, 0.05221939459443092, -1.0541198253631592, -0.0616581104695797, -0.06610167771577835, 0.13838432729244232, -0.18941067159175873, 0.3142576813697815, -0.30648788809776306, 0.16399601101875305, 0.2762434184551239, -0.30214983224868774, 0.7940282821655273, -0.013298531994223595, 0.22840838134288788, 0.0947219729423523, 0.16732759773731232, -0.1417139172554016, -0.0263410322368145, 0.013758176937699318, -0.6674084663391113, 0.7217312455177307, 0.4604962170124054, 0.3076897859573364, -0.4159224331378937, -0.004984145984053612, -0.9402560591697693, 0.2653734087944031, 0.573348343372345, -0.07820764929056168, -0.041715752333402634, 0.43161362409591675, 0.600543200969696, 0.3060205578804016, 0.5823980569839478, -0.24743078649044037, -0.2447349578142166, 0.33915358781814575, -0.39544960856437683, 0.46877384185791016, -0.22084875404834747, -0.06356673687696457, -0.24175690114498138, -0.4963257610797882, 0.6030641198158264, 0.015100132673978806, -0.27616769075393677, 0.2189474105834961, -0.14287403225898743, -0.2296183705329895, -0.05510977655649185, 0.011915135197341442, 0.3303094506263733, 0.14352314174175262, 0.6756991147994995, 0.004322570748627186, -0.42345884442329407, 0.2028825581073761, -0.6417410969734192, 0.8163884878158569, -0.47578752040863037, 0.19705864787101746, -0.3774818181991577, 1.067784070968628, -0.1532156616449356, 0.33363333344459534, -0.1467260867357254, -1.459823489189148, 0.30572906136512756, 0.3134874403476715, -0.1456182897090912, -0.1006954088807106, 0.253930926322937, -0.35083308815956116, -0.06758302450180054, 0.10609911382198334, -2.1875269412994385, 0.49603739380836487, 0.4158364534378052, -0.20911568403244019, 0.03636448085308075, -0.4276803433895111, -0.689565122127533, 0.5507440567016602, 0.09087268263101578, 0.448215514421463, -0.2660863399505615, 0.10613923519849777, 0.3008442521095276, 0.056768905371427536, 0.10691964626312256, 0.06285333633422852, -0.05542052909731865, -0.46691450476646423, -0.45762982964515686, -0.3960355222225189, -0.34848299622535706, 0.5488851070404053, 0.44295069575309753, -0.49980852007865906, 0.382076233625412, -0.4456571936607361, -0.2723846435546875, 0.8071230053901672, -0.09329113364219666, 0.3561114966869354, -0.19558680057525635, -0.43853551149368286, -0.8849593997001648, -0.06021935120224953, 0.03380998224020004, -0.116328664124012, 0.008783173747360706, -0.22345249354839325, 0.9676593542098999, 0.5571566820144653, -0.0014611432561650872, 0.1780330389738083, 0.5003000497817993, 0.5851263403892517, 0.6069217920303345, 0.21311914920806885, -0.06743566691875458, 0.8792119026184082, 0.041083354502916336, -0.6282573938369751, -0.1672814041376114, -0.4269535541534424, -0.237734854221344, -0.5129318237304688, -0.3332661986351013, -0.18714971840381622, -0.3190705478191376, 0.07364817708730698, -0.8521574139595032, 0.2409956455230713, -0.07857507467269897, 0.11875647306442261, -0.27752670645713806, -0.2568512260913849, -0.7187602519989014, -0.7297059893608093, -0.3148971498012543, -0.4719959795475006, -0.25495317578315735, 0.0501536950469017, 0.6157527565956116, 0.5345514416694641, -0.5762847661972046, 0.9138957858085632, -0.293521523475647, 0.7234703302383423, -0.15620900690555573, 0.05215044692158699, 0.7792498469352722, -0.4237942695617676, 0.448886513710022, -0.4985556900501251, -0.2162531614303589, 0.5844717621803284, -0.0909324362874031, 0.7491775751113892, 0.15449585020542145, -0.1582924723625183, -0.37785691022872925, 0.02884262055158615, -1.0098832845687866, -0.2152053862810135, -0.2694395184516907, 0.10758544504642487, 0.1550258845090866, -0.4359375834465027, 0.3679158091545105, -0.09978780895471573, -0.3573168218135834, -0.21987700462341309, -0.1290140599012375, 0.35174959897994995, 0.4060435891151428, -0.3668456971645355, 0.557102382183075, -0.10247839987277985, 0.14133593440055847, 0.42940816283226013, -0.625460684299469, 0.38848376274108887, -0.12515433132648468, -0.3209356367588043, -0.4548127055168152, -0.1048402339220047, -0.24622243642807007, -0.5348248481750488, 0.08397401124238968, -0.6145935654640198, 1.4097055196762085, 0.26541218161582947, 0.1027156263589859, -0.003816616954281926, 0.707209587097168, -0.33331164717674255, -0.11303204298019409, 0.2898455262184143, -0.5185781717300415, 0.8798075914382935, -0.675180971622467, 0.28076615929603577, -0.4890495240688324, 0.2942812144756317, 0.9887387156486511, -0.2286030352115631, 0.05808578059077263, -0.48554548621177673, -1.134573221206665, 0.5899333953857422, -0.29639530181884766, 0.1923590451478958, 0.3167372941970825, -0.2999561131000519, -0.052570611238479614, 0.5448405742645264, 0.21829570829868317, 0.052808765321969986, 0.44782736897468567, 0.9837310910224915, -0.15397684276103973, -0.6271640658378601, -0.011724160052835941, 0.35308414697647095, -1.0220004320144653, 0.5629990100860596, 0.108277827501297, -0.05188321694731712, 0.1506689041852951, 0.01008555293083191, 0.2772168815135956, -0.2905466854572296, 0.278901606798172, 0.16820548474788666, -0.36459437012672424, 0.6895487904548645, -0.34274646639823914, -0.6060948967933655, 1.010101556777954, 0.5606234669685364, -0.20874309539794922, 0.5349962711334229, -0.6381704807281494, -0.5499738454818726, 0.18166470527648926, 0.15849366784095764, -0.16848322749137878, -0.6873379349708557, -0.319710373878479, 0.12823745608329773, -0.4741123616695404, 0.5967766046524048, -0.31856802105903625, -0.26944056153297424, 0.11673643440008163, 0.4220336675643921, -0.7709693908691406, 0.03894789144396782, 0.42241230607032776, -0.6240640878677368, 0.07743410766124725, 1.1080282926559448, 0.5101504921913147, -0.018954124301671982, 0.7942858934402466, 0.6958762407302856, 0.20382308959960938, -0.2103094905614853, -0.2892463505268097, -1.6520859003067017, 0.7928376793861389, 0.3632512390613556, 0.5065745115280151, 0.22573544085025787, -0.029492707923054695, -0.1089361160993576, -0.3750343918800354, 0.29959067702293396, -0.5578228235244751, 0.4536328613758087, 0.5768368244171143, 0.13338810205459595, -0.08040228486061096, 0.07013875246047974, -0.029656754806637764, 0.13649001717567444, -0.4374179244041443, -0.3773000240325928, -0.026959512382745743, 0.3797452747821808, 0.31700944900512695, -0.6376341581344604, -0.4256746768951416, -0.2647545337677002, 0.8860739469528198, -0.26925769448280334, -0.4503996670246124, -0.20334118604660034, 0.5968058109283447, -0.17615258693695068, 0.4682821035385132, -0.1872171014547348, -0.405595988035202, 0.37801384925842285, -0.19112573564052582, -0.5325847268104553, 0.16500596702098846, 0.606103777885437, -0.7131474018096924, 0.014509514905512333, 0.9794188737869263, 0.2695803940296173, 0.2624457776546478, -0.07379456609487534, -0.061307769268751144, 0.33250972628593445, -0.03914361074566841, 0.28222113847732544, -0.2581616938114166, 0.4125804007053375, -0.06986512243747711, 0.6623756289482117, -0.7576265335083008, 0.2313765585422516, 0.03461823984980583, -0.6090500950813293, 0.09450580179691315, -0.16255803406238556, -0.5726449489593506, -0.16521595418453217, 0.31193456053733826, -0.5640338659286499, 0.11670254915952682, 0.6659051179885864, -0.2788637578487396, 0.15980300307273865, 0.5016247630119324, -0.08468235284090042, -0.453850656747818, -0.4412669539451599, 0.10220848768949509, 0.32509294152259827, 0.3434332311153412, -0.27812179923057556, -0.09959807991981506, 0.7353811860084534, -0.09830755740404129, -0.2863754332065582, -0.38493606448173523, -0.30964958667755127, 0.25637272000312805, 0.3214666545391083, 0.3651556074619293, 0.08757216483354568, -5.1007890701293945, -0.056177593767642975, -0.750350832939148, -0.5265793800354004, 0.20773839950561523, -0.5964337587356567, -0.03948325291275978, -0.22189702093601227, 0.4231422543525696, -0.6798479557037354, 0.15877175331115723, 0.513088047504425, -0.5864140391349792, -0.08915877342224121, 0.32514452934265137, 0.3218878209590912]</t>
+          <t>['high', 'medium', 'high', 'high', 'high', 'high']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[-0.5, -0.5, 0.0, 0.5, -1.0, -1.0]</t>
+          <t>['black', 'black', 'other', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[5, 3, 5, 4, 4, 5]</t>
+          <t>[30.0, 30.0, 55.0, 35.0, 30.0, 45.0]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['black', 'black', 'other', 'white', 'white', 'white']</t>
+          <t>['man', 'woman', 'man', 'woman', 'man', 'woman']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[30.0, 30.0, 55.0, 35.0, 30.0, 45.0]</t>
+          <t>[1, 1, 2, 1, 3, 1]</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>['man', 'woman', 'man', 'woman', 'man', 'woman']</t>
+          <t>[5, 4, 5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 3, 1]</t>
+          <t>[5, 4, 2, 5, 5, 3]</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>[5, 4, 5, 5, 5, 5]</t>
+          <t>[5, 5, 5, 5, 4, 5]</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>[5, 4, 2, 5, 5, 3]</t>
+          <t>[5, 1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5, 4, 5]</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>[5, 1, 2, 1, 1, 1]</t>
-        </is>
+          <t>[5, 2, 2, 5, 5, 3]</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>6</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>[5, 2, 2, 5, 5, 3]</t>
+          <t>[5, 4, 2, 5, 5, 4]</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>[5, 4, 2, 5, 5, 4]</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
           <t>[0.         0.16666667 0.         0.33333333 0.5       ]</t>
         </is>
       </c>
-      <c r="T6" t="n">
+      <c r="S6" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -1031,85 +991,78 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 5, 2, 5]</t>
+          <t>['Black american', '{}', '{}', '{}', '{}', nan]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['Black american', '{}', '{}', '{}', '{}', nan]</t>
+          <t>['left', 'left', 'right', 'right', 'far left', 'far left']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[0.04868575558066368, 0.5501320958137512, -0.18618066608905792, -0.1572660505771637, -0.3718382716178894, -0.6179807186126709, 0.5056614279747009, 0.3748174011707306, -0.03334154933691025, -0.03276948630809784, 0.003426854033023119, -0.0776345506310463, -0.10808316618204117, 0.3787849545478821, 0.3362421691417694, -0.04338954761624336, -0.21761485934257507, 0.5305992364883423, 0.28133201599121094, -0.08965796232223511, 0.10599147528409958, -0.12210872769355774, 0.04518742114305496, -0.12010776996612549, -0.04418115317821503, -0.2744404077529907, 0.08799701184034348, -0.1908002346754074, -0.05842990428209305, 0.1285284161567688, 0.035501278936862946, -0.014427326619625092, 0.14620991051197052, -0.12830597162246704, -0.08275662362575531, -0.07762801647186279, -0.061619095504283905, 0.15650580823421478, 0.22171612083911896, -0.1128062829375267, -0.07441698759794235, 0.010294648818671703, -0.031047923490405083, 0.13689199090003967, 0.15657855570316315, -0.3617769479751587, -2.3405778408050537, -0.11453133821487427, -0.019773155450820923, -0.28669995069503784, 0.4394298493862152, 0.09903623908758163, 0.1983529031276703, 0.028670866042375565, 0.21892620623111725, 0.24905459582805634, -0.564805269241333, 0.4855112135410309, -0.0026005692780017853, 0.022958872839808464, 0.07006216794252396, 0.273933470249176, -0.02477221190929413, 0.11228491365909576, 0.26775118708610535, -0.015920082107186317, -0.06626163423061371, 0.2218616008758545, -0.32640284299850464, 0.34481486678123474, -0.33682626485824585, -0.2991567552089691, 0.3960895836353302, 0.05152926966547966, 0.020511958748102188, -0.29307714104652405, 0.03139009326696396, -0.04184706509113312, -0.2977669835090637, -0.07672329992055893, 0.25086477398872375, 0.23791751265525818, -0.07074426859617233, 0.17860081791877747, 0.08988973498344421, 0.3043932020664215, -0.3297214210033417, -0.31857937574386597, 0.3246229290962219, 0.33459025621414185, -0.09567320346832275, 0.19962762296199799, 0.026645204052329063, 0.3028413653373718, 0.4930514991283417, -0.07633399218320847, 0.25531062483787537, -0.007834050804376602, 0.20870347321033478, 0.008274904452264309, 0.32585805654525757, 0.12134852260351181, 0.186046302318573, -0.5293762683868408, 0.1696481853723526, -0.019708776846528053, 0.045644357800483704, -0.2194778025150299, 0.28480133414268494, -3.0842771530151367, 0.207376167178154, 0.3049888610839844, -0.3407082259654999, -0.3183721601963043, -0.23245872557163239, 0.5728235840797424, 0.35290148854255676, -0.31553319096565247, 0.11359700560569763, -0.14188097417354584, -0.08815908432006836, 0.5730111598968506, -0.02875189296901226, -0.02122977003455162, -4.218454705551267e-05, 0.12303027510643005, 0.1542396992444992, -0.03935438022017479, 0.2886320650577545, 0.42280682921409607, 0.24915601313114166, 0.5589836835861206, -0.03922520577907562, -0.1704564243555069, -0.10192490369081497, 0.04403761401772499, 0.07710779458284378, -0.13319751620292664, -0.031213926151394844, -0.3057009279727936, -0.10694296658039093, -0.20153480768203735, -3.222165584564209, 0.3396097719669342, 0.20613065361976624, 0.13269473612308502, -0.4941633343696594, 0.00926855020225048, 0.04258048161864281, -0.14753596484661102, 0.15566761791706085, -0.023581959307193756, -0.11156021803617477, 0.19763536751270294, -0.060672130435705185, -0.28123578429222107, 0.17466981709003448, -0.46092116832733154, 0.4109507203102112, 0.36028599739074707, 0.3617534935474396, -0.27857664227485657, 0.027606604620814323, -0.3177821636199951, -0.4621368944644928, -0.06757165491580963, 0.31581300497055054, 0.06227169930934906, 0.2516116499900818, -0.058496423065662384, -0.13198554515838623, 0.22092175483703613, 0.35843709111213684, 0.14273495972156525, 0.1572200208902359, -0.22828249633312225, -0.06050314009189606, 0.08819139748811722, 0.15402604639530182, -0.1443750560283661, -0.324266642332077, 0.28567174077033997, 0.010342147201299667, 0.2689296007156372, 0.5073673129081726, 0.15283608436584473, 0.2595983147621155, -0.2375868558883667, -0.4394466280937195, 0.42762869596481323, -0.010078375227749348, -0.2218814492225647, 0.34122440218925476, 0.08354374021291733, 0.6668207049369812, -0.03547981381416321, 0.08212953060865402, -0.5538907051086426, 0.1417696326971054, 0.4681791067123413, -0.20252780616283417, 0.07446810603141785, -0.3860556185245514, -0.07608405500650406, -0.41639575362205505, 3.959524393081665, 0.012646688148379326, 0.03289172053337097, 0.3047064244747162, 0.07587362080812454, -0.10172239691019058, -0.2571674883365631, -0.09180703014135361, -0.0488802045583725, -0.47355717420578003, -0.07825504243373871, 0.4072537124156952, 0.08190411329269409, 0.0026832784060388803, -0.0026497074868530035, 0.20054662227630615, 0.05949537456035614, -0.22182181477546692, 0.17748191952705383, 0.07779907435178757, -0.24806459248065948, -0.2985890805721283, 0.4369879364967346, 0.043577950447797775, -1.6232781410217285, 0.051615774631500244, -0.20873595774173737, -0.37350162863731384, 0.5257068872451782, -0.3475274443626404, -0.17208370566368103, -0.12426086515188217, -0.1071019172668457, 0.10960996896028519, 0.2893323600292206, 0.2563821077346802, 0.24939480423927307, 0.18359588086605072, 0.3152366578578949, -0.3900867998600006, 0.25267913937568665, 0.16845715045928955, -0.05681696534156799, 0.18833591043949127, 0.04683416709303856, 0.4648410975933075, -0.027556348592042923, -0.16548900306224823, -0.5461057424545288, 0.17289647459983826, -0.04890449717640877, 0.2053186148405075, 0.3423387110233307, -0.4969593286514282, 0.10251772403717041, -0.4705227315425873, -0.07570385932922363, -0.23860280215740204, 0.5285786986351013, -0.0009112483239732683, 0.02530556544661522, 0.19011515378952026, -0.17734631896018982, -0.04470868036150932, -0.1454095095396042, 0.035978782922029495, -0.1323830932378769, -0.5426270365715027, -4.247314929962158, 0.3049734830856323, 0.12250007688999176, 0.21150554716587067, 0.43227460980415344, -0.18587663769721985, 0.12973308563232422, -0.02884392812848091, 0.04890979081392288, -0.5530883073806763, 0.4451696276664734, 0.1465032547712326, -0.08555387705564499, 0.5194233059883118, -0.1296049803495407, 0.3310879170894623, 0.1858174055814743, -0.0005872189067304134, -0.0469769611954689, -0.1783512681722641, 0.2332286834716797, 0.19712617993354797, -0.36297881603240967, 0.1820216029882431, -0.04546121880412102, -0.21033667027950287, -0.1788286566734314, -0.01273017656058073, 0.3556998074054718, -0.22851340472698212, 0.10773759335279465, 0.09993793070316315, -0.18623581528663635, -0.18292713165283203, -0.1526302695274353, -2.3678324222564697, 0.05725972354412079, -0.3000788986682892, -0.06154033541679382, 0.09366251528263092, -0.06164003908634186, 0.39767196774482727, -0.26810839772224426, -0.5426318049430847, -0.028038324788212776, -0.08626752346754074, 0.15073567628860474, -0.09928382933139801, 0.22763238847255707, 0.321180522441864, -0.2683873176574707, 0.284493625164032, -0.18720808625221252, 0.46874791383743286, 0.03515637665987015, -0.080624520778656, 0.17028488218784332, -0.18605047464370728, -0.03978322446346283, 0.08705493062734604, 0.487762451171875, -0.12386177480220795, -0.26616254448890686, -0.24027520418167114, 0.12801207602024078, -0.09201861917972565, -0.395450621843338, -0.05456630885601044, 0.1429874747991562, -0.3366304934024811, -0.6426857113838196, 0.035633742809295654, 0.013666174374520779, -0.01655205525457859, -0.12785755097866058, 0.20124919712543488, 0.37357738614082336, 0.10844695568084717, 0.5625421404838562, 0.27311229705810547, 0.004900491330772638, -0.25234097242355347, -0.3708176016807556, 0.06357443332672119, -0.18304230272769928, -0.3356970250606537, 0.015982402488589287, 1.3345890045166016, -0.07569924741983414, -0.15800556540489197, -0.4470854699611664, 0.30128487944602966, 0.07857953011989594, 0.3884730637073517, 0.3759540021419525, 0.6668682098388672, -0.07798975706100464, 0.28677424788475037, 0.0657246857881546, -0.14118903875350952, -0.3220475912094116, 0.12846630811691284, -0.6264395117759705, 0.12378478795289993, 0.05739777162671089, -0.04255670681595802, 0.026902062818408012, -0.344087153673172, -0.8103811144828796, 0.0797375962138176, 0.1577737033367157, -0.13758578896522522, 0.06009483337402344, 0.26254019141197205, 0.02767237275838852, -0.21895383298397064, -0.11011093109846115, -0.31103751063346863, 0.164870023727417, -0.14851731061935425, -0.05359850823879242, -0.13713930547237396, 0.32209619879722595, -0.21942096948623657, 0.18134750425815582, -0.05190114304423332, 0.17933739721775055, -0.19834882020950317, 0.24618245661258698, -0.20809730887413025, 0.39387425780296326, 0.09168317914009094, -0.8118032217025757, 0.05512479692697525, -0.10656209290027618, -0.5657520294189453, -0.2958545982837677, -0.0012387646129354835, 0.07026640325784683, 0.05648082122206688, -0.1352640688419342, -0.07487507909536362, 0.26182931661605835, -0.30624452233314514, 0.6220270991325378, -0.09206221252679825, 0.14015401899814606, -0.10127660632133484, 0.1599046289920807, 0.7006180286407471, -0.10040994733572006, 0.013823837973177433, 0.4344712495803833, 0.13076035678386688, 0.23216325044631958, 0.3032642602920532, -0.17500759661197662, -0.15360787510871887, -0.0025561568327248096, -0.442613810300827, -0.09226462990045547, 0.23207853734493256, -0.21839232742786407, -0.17666879296302795, -0.2975907325744629, 0.24242207407951355, 0.03045247681438923, -0.3086909055709839, -0.44402003288269043, -0.1408289670944214, -0.3058381974697113, -0.42908570170402527, 0.1607273519039154, 0.08293545991182327, 0.028333313763141632, 0.24994151294231415, 0.062249623239040375, -0.4052870273590088, 0.23232434689998627, -0.29118430614471436, 0.4333826005458832, -0.09500957280397415, 0.28340834379196167, 0.027594583109021187, 0.43001165986061096, 0.0883735865354538, -0.2870393991470337, -0.16385751962661743, -0.2195669263601303, 0.1006469875574112, 0.38913989067077637, 0.054200686514377594, -0.06569478660821915, 0.07786443084478378, 0.1437423974275589, 0.021059026941657066, 0.28663697838783264, -1.6151167154312134, 0.23219792544841766, 0.7122233510017395, -0.12246130406856537, 0.2518940269947052, 0.09485574066638947, -0.46533364057540894, 0.6647900342941284, -0.23387303948402405, 0.22210177779197693, 0.05422097444534302, 0.2548344135284424, 0.19913829863071442, -0.19295066595077515, -0.09711857885122299, 0.37911924719810486, 0.4802188277244568, -0.3151780366897583, -0.08143163472414017, 0.2312314808368683, -0.29906076192855835, 0.5209178924560547, -0.18541556596755981, -0.03866563364863396, -0.1167471781373024, -0.10874560475349426, 0.0030223079957067966, 0.4874727129936218, -0.0962899848818779, 0.14898306131362915, 0.027750136330723763, -0.23335304856300354, -0.5887866020202637, -0.2452586591243744, 0.06954313814640045, -0.07145315408706665, 0.22096659243106842, 0.3477766513824463, 0.13280244171619415, 0.5314850211143494, -0.11550073325634003, 0.321074515581131, 0.27737143635749817, -0.1886581927537918, 0.25501903891563416, 0.16931895911693573, -0.20658162236213684, 0.3938567340373993, -0.09008581936359406, -0.32011866569519043, -0.06815600395202637, 0.17536066472530365, -0.21147312223911285, -0.32677188515663147, 0.0930904969573021, -0.08605081588029861, -0.10673121362924576, 0.12244344502687454, -0.10040360689163208, 0.14985324442386627, 0.15724843740463257, 0.12517665326595306, -0.2825799584388733, 0.19066153466701508, -0.122377909719944, -0.47898977994918823, 0.06805814057588577, -0.31821030378341675, -0.21186327934265137, 0.36862775683403015, 0.505074143409729, 0.32618552446365356, -0.18684369325637817, 0.11998557299375534, -0.32577037811279297, 0.3983019292354584, 0.1872793734073639, 0.346403568983078, 0.5008228421211243, 0.06356609612703323, 0.04595956206321716, -0.3522792458534241, -0.15303324162960052, 0.08185254037380219, 0.21527965366840363, -0.06928566098213196, -0.004815880674868822, -0.20267918705940247, -0.09836050122976303, -0.03997674211859703, -0.6358782649040222, -0.19306135177612305, 0.5867979526519775, -0.1505519151687622, 0.22769784927368164, 0.129030242562294, 0.22638976573944092, -0.20595596730709076, -0.16043122112751007, 0.053394418209791183, -0.10656847804784775, 0.45713141560554504, 0.3466585576534271, -0.02028675377368927, 0.14481855928897858, 0.06922119110822678, 0.2200225293636322, 0.5108221769332886, -0.4179796874523163, -0.23524737358093262, -0.3885314166545868, 0.2370668351650238, -0.17347191274166107, -0.1904151439666748, 0.08023453503847122, -0.06135007366538048, 0.234332874417305, -0.067760169506073, 2.462498903274536, 0.35234495997428894, 0.053067050874233246, -0.45184001326560974, 0.00044838819303549826, 0.04514594003558159, -0.03731779381632805, -0.03589995577931404, -0.3680148422718048, 0.5331776142120361, -0.29553428292274475, -0.015409053303301334, 0.2424475997686386, 0.14673087000846863, 0.3186686933040619, 0.14195993542671204, -0.13716541230678558, -0.47893041372299194, -0.6307657361030579, -0.29190653562545776, -0.251821368932724, -0.060673777014017105, 0.26395511627197266, -0.35040247440338135, 0.03801395744085312, 0.13061580061912537, -0.04124518856406212, 0.45333772897720337, 0.04994766414165497, 0.02010932005941868, 0.07334499061107635, -0.0884304791688919, 0.01016885694116354, 0.04323665797710419, -0.09684351086616516, 0.4372693598270416, 0.2548719644546509, -0.34231218695640564, 0.10975873470306396, -0.28903788328170776, 0.023009030148386955, -0.4228699505329132, 0.42591094970703125, 0.2888178527355194, 0.18660897016525269, 0.34989628195762634, -0.13138605654239655, -0.038397323340177536, 0.4233507812023163, 0.23237553238868713, -0.2719310522079468, 0.024868547916412354, -0.4330485165119171, 0.012710538692772388, -0.06668481975793839, -0.37036412954330444, 0.005017965566366911, -0.2976207435131073, 0.03198279067873955, 0.08493075519800186, -0.013414504006505013, 0.0576656349003315, 0.17408016324043274, 0.02474966086447239, -0.057898953557014465, 0.15838859975337982, -0.2706679105758667, 0.11545658111572266, -0.0947360023856163, -0.28591451048851013, 0.0468297116458416, 0.31044885516166687, 0.36967021226882935, -0.32519155740737915, 0.3665670156478882, -0.0041192397475242615, 0.16105309128761292, -0.12816199660301208, -0.3144104480743408, -3.398045301437378, 0.19001029431819916, -0.23405882716178894, -0.11296916753053665, 0.040022436529397964, 0.25249138474464417, 0.3127189576625824, -0.031056344509124756, 0.25752928853034973, -0.01513667032122612, 0.19829976558685303, 0.28727731108665466, 0.12169573456048965, 0.24329794943332672, 0.030189286917448044, 0.11321010440587997, 0.1637435257434845, -0.4771796762943268, -0.3289186954498291, 0.10933829098939896, 0.11123789846897125, -0.26849865913391113, 0.03044348768889904, -0.09443933516740799, -0.033326052129268646, 0.3078576624393463, 0.27818623185157776, -0.3908344507217407, -0.1234326958656311, 0.3351598381996155, -0.21436446905136108, 0.15502741932868958, -0.148176372051239, -0.06521102786064148, 0.09829846024513245, 0.11313934624195099, 0.13685737550258636, -0.25562214851379395, 0.4713671803474426, -0.03313460201025009, -0.06864195317029953, 0.3650558590888977, 0.0208306722342968, 0.09806028753519058, -0.02418944425880909, -0.25067272782325745, 0.25487828254699707, -0.20669510960578918, 0.13338132202625275, -0.28837352991104126, 0.12549807131290436, 0.013753924518823624, 0.08071321249008179, -0.06286396086215973, 0.2719762325286865, 0.09120665490627289, 0.09199674427509308, 0.10624620318412781, 0.13084915280342102, -0.24398477375507355, 0.18973799049854279, -0.1334809809923172, 0.031134935095906258, -0.01952185481786728, 0.20236025750637054, -0.177902951836586, 0.052424803376197815, 0.1788608729839325, -0.14238198101520538, -0.021730951964855194, -0.12204354256391525, 0.016362128779292107, 0.0894051268696785, 0.15326787531375885, 0.17380502820014954, 0.33297839760780334, 0.4858773946762085, 0.6211206316947937, -0.19095604121685028, 0.0027073232922703028, -0.1485716551542282, 0.023528384044766426, -0.09654106944799423, 0.27015161514282227, -0.17049388587474823, -8.498124122619629, 0.03016940876841545, -0.26090604066848755, -0.10947718471288681, 0.19243434071540833, 0.0621437169611454, -0.11438015103340149, 0.074235700070858, 0.17438150942325592, -0.027024315670132637, -0.09313898533582687, 0.06574290245771408, -0.036676838994026184, -0.3094729781150818, 0.2813848853111267, 0.39402204751968384]</t>
+          <t>['high', 'medium', 'medium', 'high', 'low', 'high']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[-0.5, -0.5, 0.5, 0.5, -1.0, -1.0]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[5, 3, 3, 4, 2, 5]</t>
+          <t>[30.0, 30.0, 35.0, 35.0, 35.0, 45.0]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['man', 'woman', 'man', 'woman', 'woman', 'woman']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[30.0, 30.0, 35.0, 35.0, 35.0, 45.0]</t>
+          <t>[1, 1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>['man', 'woman', 'man', 'woman', 'woman', 'woman']</t>
+          <t>[5, 4, 4, 5, 5, 5]</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1, 1]</t>
+          <t>[3, 4, 4, 5, 5, 5]</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>[5, 4, 4, 5, 5, 5]</t>
+          <t>[5, 5, 5, 5, 4, 3]</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>[3, 4, 4, 5, 5, 5]</t>
+          <t>[5, 1, 3, 1, 1, 1]</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5, 4, 3]</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>[5, 1, 3, 1, 1, 1]</t>
-        </is>
+          <t>[1, 4, 4, 4, 5, 5]</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>6</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>[1, 4, 4, 4, 5, 5]</t>
+          <t>[3, 3, 5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>[3, 3, 5, 5, 5, 5]</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
           <t>[0.         0.         0.33333333 0.         0.66666667]</t>
         </is>
       </c>
-      <c r="T7" t="n">
+      <c r="S7" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1129,85 +1082,78 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 2, 5, 5]</t>
+          <t>['{}', '{}', nan, '{}', '{}', '{}']</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['{}', '{}', nan, '{}', '{}', '{}']</t>
+          <t>['far left', 'center', 'far right', 'right', 'left', 'left']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[0.3449878394603729, 0.44626960158348083, 0.12818634510040283, -0.37315601110458374, -0.29393690824508667, -0.3771844506263733, 0.3797130882740021, 0.2957490384578705, -0.039208024740219116, -0.022627059370279312, 0.31579098105430603, 0.23717407882213593, -0.2994094789028168, 0.3299234211444855, 0.23935933411121368, 0.3214610815048218, -0.3104349374771118, 0.27600571513175964, 0.3331581652164459, 0.09312479197978973, 0.09852111339569092, -0.14318126440048218, -0.09831808507442474, 0.016448883339762688, 0.13436095416545868, -0.0042150323279201984, 0.1846347451210022, -0.18888147175312042, -0.4182523787021637, 0.39259958267211914, 0.00628582714125514, 0.1926732361316681, -0.13774004578590393, -0.2729152739048004, 0.40946152806282043, 0.05719074606895447, 0.08826536685228348, 0.04870709031820297, 0.07867243885993958, -0.4947015941143036, 0.07328642159700394, 0.09136616438627243, 0.21477766335010529, -0.01560360100120306, -0.16811230778694153, -0.24374988675117493, -2.8208744525909424, -0.07189375907182693, -0.2607249319553375, -0.4076388478279114, 0.14902468025684357, -0.1102510318160057, -0.17823141813278198, 0.15665318071842194, 0.4170632064342499, 0.19039541482925415, -0.20167176425457, 0.3078193962574005, 0.12610051035881042, 0.28821972012519836, 0.23219996690750122, 0.2217000126838684, -0.17818178236484528, 0.4055890440940857, -0.08650548756122589, -0.10082238167524338, 0.08895169943571091, 0.3035129904747009, -0.3128598928451538, 0.4251798093318939, -0.48978686332702637, -0.27637946605682373, 0.16205477714538574, -0.17307960987091064, -0.2131471186876297, -0.41621342301368713, -0.12409618496894836, 0.08447923511266708, -0.13674448430538177, -0.04778419807553291, 0.13970685005187988, 0.3588777482509613, -0.018841709941625595, 0.20868845283985138, -0.12154415994882584, 0.536005973815918, 0.0053629688918590546, -0.19557985663414001, 0.3938676118850708, 0.4784572124481201, -0.021126480773091316, 0.15204539895057678, -0.2700139582157135, 0.04632154852151871, 0.3307172656059265, -0.11208611726760864, 0.16256219148635864, 0.018876004964113235, 0.13787725567817688, 0.14673830568790436, 0.40333977341651917, -0.04466719925403595, -0.053130585700273514, -0.7820356488227844, 0.03889833018183708, -0.17039801180362701, 0.028245413675904274, -0.5106660723686218, 0.4984835088253021, -2.6660680770874023, 0.1874796748161316, 0.03091137856245041, -0.09522144496440887, -0.1613011360168457, -0.08427595347166061, 0.11912976205348969, 0.2409263551235199, -0.04022929072380066, 0.05354854464530945, 0.21081556379795074, -0.13258014619350433, 0.40848508477211, -0.39032182097435, -0.031049011275172234, 0.07650062441825867, 0.03477802500128746, -0.07988045364618301, 0.08684919774532318, 0.10695234686136246, 0.2326555997133255, 0.23876745998859406, 0.5903332829475403, 0.03818638622760773, -0.2904169261455536, -0.18679183721542358, 0.02361687272787094, 0.3333665430545807, -0.020453041419386864, 0.007874971255660057, -0.3504769206047058, -0.23447121679782867, -0.2035931795835495, -3.075011730194092, 0.09721717983484268, 0.2665140926837921, -0.06487957388162613, -0.3639502227306366, -0.02465915121138096, 0.07526782900094986, -0.041673868894577026, -0.03117094747722149, 0.08732786774635315, 0.18033821880817413, 0.10863456130027771, -0.07251950353384018, -0.2821339964866638, -0.11072639375925064, -0.2913239896297455, 0.11046160757541656, 0.44284772872924805, 0.3129461705684662, -0.333449125289917, 0.25729963183403015, -0.15243969857692719, -0.13675270974636078, 0.01607663556933403, 0.5920816659927368, -0.16760361194610596, 0.011784330941736698, 0.08484414219856262, 0.03156742826104164, 0.10668159276247025, 0.39222413301467896, -0.013211570680141449, 0.3626503050327301, -0.2183937430381775, 0.13944724202156067, 0.20029932260513306, 0.055857304483652115, 0.030911646783351898, -0.3661404252052307, 0.42833736538887024, 0.009260434657335281, 0.4098810851573944, 0.6171084046363831, -0.3617280125617981, 0.40684980154037476, -0.1989045888185501, -0.328167200088501, 0.26798856258392334, -0.22481653094291687, -0.2739599049091339, 0.4736309349536896, 0.14067824184894562, 0.5077199935913086, -0.215838223695755, 0.10182907432317734, -0.8658778667449951, 0.007153558079153299, 0.4127669632434845, -0.35776636004447937, 0.3362281918525696, 0.03362136334180832, -0.26706740260124207, -0.2105652242898941, 4.299838542938232, 0.1779702603816986, 0.06205964460968971, -0.06462638080120087, 0.02747100032866001, -0.1643451601266861, -0.2803393006324768, -0.2511362135410309, -0.43580958247184753, -0.41356414556503296, -0.1402634084224701, 0.3342553675174713, 0.10041540116071701, -0.24637334048748016, -0.3221316933631897, 0.06925680488348007, 0.5377644300460815, -0.15076817572116852, 0.31357893347740173, 0.01326197199523449, -0.17155788838863373, -0.20696379244327545, 0.09578835219144821, 0.025687936693429947, -1.8303570747375488, 0.07927366346120834, -0.02846464328467846, -0.4651830494403839, 0.3992495536804199, 0.058769188821315765, 0.016417505219578743, 0.0721878781914711, -0.012288190424442291, 0.07924447953701019, 0.2591257393360138, 0.1110609844326973, 0.18580974638462067, 0.12278231233358383, 0.061325158923864365, -0.5197252035140991, 0.18458761274814606, 0.11943292617797852, -0.12679001688957214, 0.09615135192871094, 0.18626326322555542, -0.04032476991415024, 0.3898250162601471, -0.11241189390420914, -0.29619842767715454, 0.217502623796463, 0.13989436626434326, -0.10650704801082611, 0.49134477972984314, -0.1725671887397766, -0.3168082535266876, -0.4733321964740753, 0.019332533702254295, -0.23342488706111908, 0.2834002375602722, -0.2650008499622345, -0.15971681475639343, 0.054822396486997604, -0.2112862765789032, -0.2548501193523407, 0.11810462921857834, 0.10109031945466995, -0.19769863784313202, -0.28747233748435974, -4.014257907867432, -0.040200576186180115, 0.07518183439970016, 0.3151226043701172, 0.3720757067203522, -0.32970622181892395, -0.009132549166679382, 0.23901771008968353, 0.1514413058757782, -0.4764317572116852, 0.2922961711883545, 0.018158255144953728, -0.10125336050987244, 0.5109025835990906, -0.1784040927886963, 0.1464242786169052, 0.3246040344238281, 0.1259336769580841, 0.10327805578708649, -0.28473377227783203, 0.26595833897590637, 0.21756288409233093, -0.49632972478866577, 0.016440793871879578, -0.16339002549648285, -0.08128617703914642, -0.3878689110279083, -0.0788009837269783, 0.41751930117607117, -0.042094603180885315, 0.03613653779029846, 0.14826397597789764, -0.4593992829322815, -0.20884071290493011, -0.19197365641593933, -3.0397167205810547, 0.018654830753803253, -0.37394946813583374, -0.18366985023021698, 0.2946327030658722, -0.03456758335232735, 0.659421980381012, -0.27518847584724426, -0.598894476890564, 0.12474706768989563, -0.038945142179727554, 0.2161446213722229, -0.2667248249053955, -0.15479664504528046, 0.2597804665565491, 0.085073322057724, 0.46381258964538574, -0.24066738784313202, 0.5709388852119446, 0.10501179844141006, -0.13931383192539215, 0.1930037885904312, -0.12576650083065033, 0.037014879286289215, -0.09012115001678467, 0.329348623752594, -0.4399724304676056, -0.315637469291687, 0.07391690462827682, 0.14656779170036316, -0.11844053864479065, -0.23004184663295746, -0.12156042456626892, 0.07255425304174423, -0.20865802466869354, -0.6036192774772644, 0.021553805097937584, 0.1791265606880188, 0.2195807844400406, -0.25214600563049316, 0.1035614013671875, 0.618084728717804, -0.24369990825653076, 0.22823303937911987, 0.2925357222557068, -0.17539751529693604, -0.039645615965127945, -0.362688273191452, -0.05185885354876518, 0.008134989999234676, 0.070575051009655, 0.4608180820941925, 1.183478832244873, 0.00622272863984108, -0.21390283107757568, -0.2902660369873047, 0.2276177853345871, 0.26833778619766235, 0.3125205934047699, 0.35327115654945374, 0.7133798003196716, -0.4783497452735901, 0.33654123544692993, -0.03247635439038277, 0.007327839732170105, -0.05679740011692047, 0.31093350052833557, -0.4917159080505371, 0.21767310798168182, -0.14914412796497345, -0.08495382964611053, -0.23160988092422485, -0.5387018918991089, -1.1105966567993164, 0.20597542822360992, 0.3969476819038391, -0.10152951627969742, 0.12109760195016861, 0.15361353754997253, -0.06059814989566803, -0.001536648371256888, -0.12244421243667603, -0.06679737567901611, 0.23840850591659546, -0.4035671055316925, -0.33049848675727844, -0.29100945591926575, 0.34975430369377136, -0.18193288147449493, 0.3202318847179413, -0.026525162160396576, 0.003878567833453417, -0.06263355165719986, 0.14530950784683228, 0.13238981366157532, 0.4370272159576416, 0.031468044966459274, -0.6646773815155029, 0.09687300026416779, -0.23974452912807465, -0.4316041171550751, -0.2784788906574249, -0.16868789494037628, 0.047639768570661545, -0.05320480465888977, -0.3736037313938141, 0.04104097932577133, 0.718272864818573, -0.05016013979911804, 0.23408746719360352, 0.10786858201026917, 0.2681905925273895, -0.1004088968038559, 0.08737847208976746, 0.6579422354698181, -0.28823724389076233, -0.24268925189971924, 0.42415252327919006, 0.04242862015962601, 0.002206843113526702, 0.4937126040458679, 0.20173941552639008, -0.25990620255470276, -0.24797599017620087, -0.15251114964485168, -0.03110749088227749, 0.12661151587963104, 0.029364988207817078, -0.06949955970048904, -0.37124356627464294, 0.024977898225188255, -0.014315305277705193, -0.3869689702987671, -0.5251065492630005, -0.19475194811820984, -0.2593328058719635, -0.5335060358047485, 0.05150412768125534, 0.14008601009845734, -0.0336620919406414, 0.3636825680732727, 0.33255016803741455, -0.015164073556661606, 0.16342778503894806, -0.3658018708229065, 0.4323374330997467, -0.12215709686279297, 0.29654020071029663, 0.018101079389452934, 0.1942029595375061, -0.07555808126926422, 0.3048669695854187, -0.24492983520030975, -0.5863625407218933, 0.22191321849822998, 0.40712133049964905, -0.1973201036453247, 0.16348260641098022, 0.011843103915452957, -0.14035636186599731, 0.4133496582508087, 0.18771804869174957, -2.057757616043091, 0.5235885381698608, 0.6984144449234009, 0.1032181978225708, 0.3638598322868347, -0.31574520468711853, -0.3871500790119171, 0.42960813641548157, 0.09867268800735474, 0.28398677706718445, -0.2375752180814743, 0.16845868527889252, -0.12183557450771332, 0.15730425715446472, 0.20931534469127655, 0.16734328866004944, 0.6494887471199036, -0.3867436647415161, -0.10003701597452164, 0.015349381603300571, 0.048500269651412964, 0.06957648694515228, -0.26381221413612366, -0.038916245102882385, -0.16048353910446167, 0.06946452707052231, 0.10835403949022293, 0.3199795186519623, 0.08212296664714813, 0.3230414092540741, 0.1559557467699051, -0.24870388209819794, -0.4885481595993042, -0.3481886684894562, 0.33918458223342896, 0.12390417605638504, 0.07679850608110428, -0.0030789379961788654, 0.5547844767570496, 0.414894163608551, -0.37522152066230774, 0.06432408094406128, 0.4332301914691925, 0.21089428663253784, 0.11857347190380096, 0.22178834676742554, -0.24958986043930054, 0.260687917470932, 0.12522192299365997, -0.4772872030735016, -0.2764641344547272, 0.13913162052631378, -0.2624940872192383, -0.35725757479667664, 0.12176665663719177, -0.4680190980434418, -0.08086918294429779, 0.02346612513065338, -0.45401015877723694, 0.10686930269002914, 0.07013221830129623, 0.21395035088062286, -0.4072171747684479, 0.15614712238311768, -0.3466404676437378, -0.5216519832611084, 0.0007700870628468692, -0.10964000225067139, -0.4219348430633545, 0.6164955496788025, 0.3099838197231293, 0.3281938433647156, -0.43202587962150574, 0.3404140770435333, -0.1252059042453766, 0.5327924489974976, 0.11242993175983429, 0.11098253726959229, 0.34876590967178345, 0.15281961858272552, 0.20309825241565704, -0.5084653496742249, -0.2022663801908493, 0.38707268238067627, 0.05595279484987259, 0.1843377947807312, -0.055289458483457565, -0.18678630888462067, 0.14327336847782135, 0.030564704909920692, -0.5353848934173584, -0.4111250340938568, 0.23500224947929382, 0.1598317176103592, 0.06895458698272705, 0.047110747545957565, 0.2072504162788391, -0.27283379435539246, -0.1647007018327713, 0.25105515122413635, -0.19318130612373352, 0.30136746168136597, 0.5447375178337097, 0.1031566858291626, -0.001891177031211555, 0.04777951166033745, 0.017248885706067085, 0.1571175903081894, -0.5426260828971863, -0.138367161154747, 0.33590203523635864, 0.3746928870677948, 0.061886150389909744, -0.14250406622886658, 0.09672088176012039, -0.4110983610153198, 0.7441958785057068, -0.3962336480617523, 2.252260684967041, 0.2953980565071106, -0.10268395394086838, -0.38851508498191833, 0.3384501039981842, -0.09948476403951645, 0.09502772986888885, -0.05099020153284073, -0.11457206308841705, 0.4320827126502991, -0.17378462851047516, 0.20997288823127747, -0.22411267459392548, -0.12923866510391235, 0.39379754662513733, 0.43851473927497864, -0.14932292699813843, -0.6030218601226807, -0.5062311291694641, 0.09098803251981735, 0.0068701584823429585, 0.26735207438468933, 0.11887531727552414, -0.27394482493400574, 0.04214399680495262, 0.2708016633987427, 0.10947310924530029, 0.20963715016841888, 0.25463926792144775, 0.11446446925401688, -0.30532005429267883, -0.05079551786184311, 0.07739183306694031, 0.2207031399011612, -0.11700236052274704, 0.1839638352394104, 0.48982957005500793, -0.2233799546957016, 0.17599588632583618, -0.05625920370221138, -0.18721580505371094, -0.18218977749347687, 0.585626482963562, 0.09720253944396973, 0.20301197469234467, 0.26075464487075806, 0.044079698622226715, -0.1976899951696396, 0.37393665313720703, 0.28977835178375244, -0.15862616896629333, 0.18647730350494385, -0.182732954621315, -0.02203245460987091, -0.01258857361972332, -0.10334154218435287, 0.018316080793738365, -0.27991583943367004, -0.003768655937165022, 0.21089251339435577, -0.4734301269054413, 0.07284994423389435, 0.043489404022693634, 0.04475858807563782, -0.07124955207109451, 0.11345326900482178, -0.16289664804935455, 0.03875651955604553, 0.15428520739078522, -0.306138813495636, -0.04430609941482544, 0.1524287611246109, 0.18291574716567993, -0.06615050137042999, 0.41400641202926636, 0.4428049921989441, 0.14750662446022034, 0.15010178089141846, -0.3087317943572998, -3.0144388675689697, 0.241594135761261, -0.04414093866944313, -0.08826787769794464, -0.045243460685014725, 0.26177772879600525, 0.256130188703537, -0.20607848465442657, 0.05946074798703194, 0.06592922657728195, 0.3354334533214569, 0.4498251676559448, 0.23881320655345917, 0.11935197561979294, 0.06597129255533218, -0.07762282341718674, -0.060395292937755585, -0.4215460419654846, -0.07228660583496094, 0.12323372811079025, 0.31344765424728394, -0.004702052567154169, -0.2543275058269501, -0.386044979095459, 0.030188731849193573, 0.3177608847618103, 0.44086331129074097, -0.2958497405052185, -0.0378577783703804, -0.02806413546204567, 0.17908111214637756, -0.19910284876823425, -0.025841714814305305, -0.26958534121513367, 0.3339734971523285, -0.013359876349568367, -0.2683092951774597, -0.13908767700195312, 0.18106386065483093, 0.038301508873701096, 0.08797664195299149, 0.7141254544258118, 0.08598995953798294, -0.08428425341844559, 0.06312109529972076, -0.13218262791633606, 0.4728270471096039, -0.3475841283798218, 0.4420849680900574, -0.059187501668930054, 0.1393929272890091, -0.07518544048070908, -0.07587912678718567, 0.34093987941741943, 0.38344767689704895, 0.16496630012989044, 0.26550397276878357, -0.003015513066202402, 0.12928703427314758, -0.02400883287191391, 0.10164837539196014, 0.026395076885819435, -0.287564218044281, -0.16576234996318817, 0.01755930297076702, -0.05048779398202896, 0.19258221983909607, 0.14322130382061005, -0.23892034590244293, -0.21934805810451508, 0.114255890250206, 0.10732900351285934, 0.3948797583580017, 0.09152195602655411, -0.043648671358823776, 0.06611267477273941, 0.36401405930519104, 0.24590370059013367, 0.17320993542671204, -0.293377161026001, 0.04252864047884941, 0.2072543203830719, -0.07295409590005875, 0.1660776138305664, 0.17035339772701263, -7.588127136230469, -0.24478478729724884, 0.06386370211839676, -0.26455458998680115, -0.19354161620140076, -0.043280694633722305, -0.1834394335746765, -0.3591610789299011, -0.16834452748298645, -0.0905100628733635, 0.15114031732082367, 0.10476820915937424, -0.160749152302742, -0.5992478728294373, 0.4812188744544983, 0.5698426365852356]</t>
+          <t>['high', 'high', 'medium', 'high', 'high', 'medium']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[-1.0, 0.0, 1.0, 0.5, -0.5, -0.5]</t>
+          <t>['black', 'black', 'white', 'hisp', 'white', 'white']</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[5, 4, 3, 5, 5, 3]</t>
+          <t>[25.0, 35.0, 35.0, 30.0, 35.0, 45.0]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'hisp', 'white', 'white']</t>
+          <t>['woman', 'man', 'man', 'man', 'woman', 'woman']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>[25.0, 35.0, 35.0, 30.0, 35.0, 45.0]</t>
+          <t>[3, 1, 5, 3, 1, 2]</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>['woman', 'man', 'man', 'man', 'woman', 'woman']</t>
+          <t>[5, 4, 1, 5, 5, 3]</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>[3, 1, 5, 3, 1, 2]</t>
+          <t>[3, 5, 5, 2, 5, 4]</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>[5, 4, 1, 5, 5, 3]</t>
+          <t>[5, 4, 5, 4, 4, 3]</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>[3, 5, 5, 2, 5, 4]</t>
+          <t>[4, 1, 5, 1, 1, 2]</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>[5, 4, 5, 4, 4, 3]</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>[4, 1, 5, 1, 1, 2]</t>
-        </is>
+          <t>[4, 5, 5, 1, 5, 4]</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>6</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>[4, 5, 5, 1, 5, 4]</t>
+          <t>[5, 5, 4, 1, 5, 5]</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>[5, 5, 4, 1, 5, 5]</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
           <t>[0.16666667 0.         0.         0.16666667 0.66666667]</t>
         </is>
       </c>
-      <c r="T8" t="n">
+      <c r="S8" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -1227,85 +1173,78 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[4, 2, 4, 5, 5, 5]</t>
+          <t>['{}', '{}', '{}', 'None', 'immigrant', '{}']</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['{}', '{}', '{}', 'None', 'immigrant', '{}']</t>
+          <t>['left', 'left', 'right', 'right', 'left', 'far left']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[-0.19164827466011047, 0.24510705471038818, 0.07372259348630905, -0.20038162171840668, -0.4582807719707489, -0.408297061920166, 0.6677278876304626, 0.8496958613395691, 0.06635136902332306, -0.0910836011171341, 0.09753572940826416, -0.0895056426525116, -0.5154240727424622, 0.48673298954963684, 0.3210696280002594, 0.30378586053848267, -0.30976855754852295, 0.20589853823184967, 0.512686014175415, 0.16806423664093018, -0.1396131068468094, -0.3748125731945038, 0.18606840074062347, -0.26563000679016113, -0.10132645070552826, -0.20218290388584137, 0.14599157869815826, -0.04506443813443184, -0.05629532411694527, 0.12002607434988022, 0.01832800731062889, 0.2692866921424866, -0.2753032147884369, -0.2158203423023224, 0.3680790364742279, 0.23139068484306335, 0.4021678864955902, 0.022723982110619545, 0.2251298576593399, 0.338165819644928, -0.41460368037223816, -0.062170062214136124, -0.0020712357945740223, -0.03281715139746666, -0.039276473224163055, -0.5342500805854797, -2.97800350189209, -0.04374920204281807, 0.05129103362560272, -0.2438075840473175, 0.3796778619289398, -0.38566505908966064, -0.170058935880661, 0.3895868957042694, 0.23220416903495789, 0.40029218792915344, -0.3867444097995758, 0.0034269497264176607, 0.19734874367713928, 0.3645460605621338, 0.5193750262260437, 0.06999260187149048, -0.11555616557598114, -0.12672658264636993, 0.12462284415960312, -0.029693707823753357, -0.30668139457702637, 0.7084790468215942, -0.8602574467658997, 0.17334896326065063, -0.507513165473938, -0.136875182390213, 0.195960134267807, 0.0537654384970665, -0.01338244043290615, -0.29246413707733154, -0.06074024364352226, 0.2741246521472931, -0.5375352501869202, -0.009436435997486115, -0.19097617268562317, 0.4506327211856842, -0.10232196003198624, 0.008452984504401684, -0.19085398316383362, 0.7048638463020325, -0.25650015473365784, -0.16138510406017303, 0.12607578933238983, -0.08179298788309097, 0.2954972982406616, 0.14499814808368683, -0.20797894895076752, 0.10083570331335068, 0.4527116119861603, 0.08576269447803497, 0.19984081387519836, 0.22489379346370697, 0.19469290971755981, 0.29527491331100464, 0.525519847869873, 0.3212319314479828, 0.16017572581768036, -0.5874785780906677, 0.28380024433135986, -0.2477729320526123, 0.17378990352153778, -0.08910755813121796, 0.46266669034957886, -2.8064072132110596, 0.5216113924980164, 0.18998970091342926, -0.14160209894180298, -0.30620768666267395, -0.12218071520328522, 0.37652549147605896, 0.37594494223594666, -0.4659824073314667, 0.1406458616256714, 0.33486849069595337, -0.4454832375049591, 0.27796804904937744, -0.22072148323059082, 0.09391047805547714, 0.2760717570781708, 0.3961372375488281, 0.10438507050275803, 0.09217974543571472, 0.273657888174057, 0.6497241854667664, 0.08846826106309891, 0.37763890624046326, 0.05365518108010292, -0.47505131363868713, -0.32111749053001404, -0.0888824611902237, 0.40061813592910767, -0.2357919067144394, -0.1391202211380005, -0.028890460729599, -0.3930269479751587, -0.8217236995697021, -3.23081374168396, 0.2566516697406769, 0.3779686987400055, 0.27266228199005127, -0.5297287702560425, -0.118682861328125, 0.0383390448987484, 0.048139024525880814, -0.024661172181367874, -0.33573636412620544, 0.32887476682662964, 0.386528879404068, -0.2835957407951355, -0.05646994709968567, -0.036053113639354706, -0.21042266488075256, 0.008943824097514153, 0.6449427008628845, 0.3201097249984741, -0.04210750386118889, 0.020604455843567848, -0.019778577610850334, 0.08500909805297852, -0.26751911640167236, 0.014086440205574036, 0.5136634707450867, -0.20732738077640533, -0.15752685070037842, -0.3440001904964447, 0.3684103488922119, 0.8627016544342041, 0.052763763815164566, 0.1502290517091751, -0.4066465497016907, 0.23819780349731445, 0.22023515403270721, -0.08411471545696259, -0.14366258680820465, -0.3337234556674957, 0.136945903301239, 0.35408714413642883, 0.5513357520103455, 0.3885534107685089, -0.010680193081498146, 0.47991517186164856, 0.02768395096063614, -0.3532734215259552, 0.3423558473587036, -0.2917768657207489, -0.30890706181526184, 0.46552973985671997, 0.6151930689811707, 0.6338684558868408, -0.2022789716720581, -0.2972722053527832, -0.6612265110015869, 0.2694763243198395, 0.2668040990829468, 0.13317282497882843, -0.10078705102205276, -0.025287248194217682, 0.11496683955192566, -0.6205362677574158, 3.96030330657959, 0.2337723970413208, -0.17516091465950012, 0.5361489653587341, 0.5501111149787903, -0.07987645268440247, 0.11673307418823242, -0.46701478958129883, -0.17773136496543884, -0.35265257954597473, 0.13649435341358185, 0.3794156014919281, 0.22073988616466522, -0.19241516292095184, 0.24397531151771545, -0.005415416322648525, 0.2893853783607483, -0.18150418996810913, 0.39924466609954834, -0.030209872871637344, 0.17962084710597992, -0.257639080286026, 0.06461244821548462, 0.1263403743505478, -1.658042311668396, 0.19415497779846191, -0.13646726310253143, -0.25193843245506287, 0.17448240518569946, -0.25756433606147766, 0.4334106147289276, -0.06735260039567947, -0.3217914402484894, 0.08505436778068542, 0.10777640342712402, 0.1217767745256424, 0.5026577115058899, 0.1723981499671936, 0.056534454226493835, 0.060660529881715775, 0.35113587975502014, -0.0018667071126401424, -0.6985492706298828, 0.03644164651632309, 0.4569874107837677, 0.2708158493041992, -0.315421998500824, 0.03432556986808777, -0.6844878792762756, 0.06224264204502106, 0.16615641117095947, 0.13088847696781158, 0.33246058225631714, -0.5974152088165283, -0.3841339349746704, 0.03479566052556038, 0.02551409974694252, -0.12608638405799866, 0.3522259593009949, -0.40842363238334656, -0.39535725116729736, -0.38212358951568604, -0.04503502696752548, -0.39187800884246826, 0.014231951907277107, 0.2606249451637268, -0.19053766131401062, 0.04915407672524452, -3.4396400451660156, 0.4547640085220337, 0.2016143649816513, 0.09723825007677078, 0.37788400053977966, -0.21445274353027344, -0.14231088757514954, 0.103672094643116, 0.08816767483949661, -0.5292252898216248, 0.6366311311721802, 0.20433861017227173, -0.12620343267917633, 0.4847014546394348, 0.1634742021560669, 0.2611822783946991, 0.037551991641521454, 0.1564481407403946, -0.3110799193382263, 0.014466939494013786, 0.3516365587711334, 0.24826237559318542, -0.3114126920700073, 0.026865767315030098, 0.03104257769882679, 0.02548336610198021, -0.27552172541618347, -0.37645700573921204, 0.4864034056663513, -0.4843858778476715, 0.35214099287986755, 0.04512971639633179, -0.16359412670135498, -0.07790780812501907, -0.6437246799468994, -2.877007484436035, 0.2884202301502228, 0.00296395318582654, -0.44113409519195557, -0.08072967082262039, -0.1764223426580429, 0.5860447287559509, -0.4194130003452301, -0.6206190586090088, -0.21489456295967102, 0.3270544111728668, 0.13214263319969177, 0.09336012601852417, 0.00033401354448869824, 0.16899532079696655, 0.49334487318992615, 0.2814003527164459, -0.20098312199115753, 0.19879060983657837, -0.03244621679186821, 0.061018213629722595, 0.3014950454235077, -0.053576018661260605, 0.1248147115111351, 0.14030957221984863, -0.0386611670255661, -0.3928675055503845, -0.10276921838521957, 0.3525623083114624, 0.04176371544599533, 0.21291689574718475, 0.27892792224884033, 0.036369048058986664, -0.14963601529598236, -0.22574537992477417, -0.22393092513084412, 0.35870257019996643, 0.013616698794066906, 0.24648280441761017, -0.09049645066261292, 0.22166885435581207, 0.4827924370765686, -0.07554496824741364, 0.19156226515769958, 0.6840553879737854, -0.20460566878318787, -0.3661491274833679, -0.5311529636383057, -0.205900177359581, -0.08667854219675064, -0.11808137595653534, -0.3067430853843689, 0.7030326128005981, -0.1789092868566513, -0.23675106465816498, -0.09648378938436508, 0.43211814761161804, 0.18869329988956451, 0.2765704095363617, -0.23885849118232727, 0.6935006976127625, -0.2730972170829773, 0.10939999669790268, -0.14568647742271423, 0.11637827754020691, -0.16243353486061096, 0.3593973219394684, -0.6317253708839417, 0.1518843173980713, 0.24908359348773956, -0.056000277400016785, 0.5505136251449585, -0.2620927095413208, -1.0807931423187256, -0.20979411900043488, 0.2712096869945526, -0.24283914268016815, 0.1429419368505478, -0.06178032234311104, 0.11952506750822067, 0.1052401140332222, 0.10971241444349289, 0.0007157486979849637, 0.3128108084201813, -0.5446073412895203, 0.002652029739692807, 0.054550424218177795, 0.3232300281524658, -0.8282983303070068, -0.013339545577764511, -0.2313816398382187, 0.26026010513305664, -0.16922634840011597, 0.1945015788078308, -0.12262384593486786, 0.27016308903694153, 0.5596623420715332, -0.5935025215148926, 0.19407351315021515, -0.3867284953594208, 0.18819886445999146, -0.23583759367465973, 0.14081569015979767, -0.3173152506351471, 0.04267165809869766, -0.01801098883152008, -0.22143951058387756, 0.6399174928665161, -0.5076821446418762, 0.2938845157623291, -0.1504426747560501, 0.059579987078905106, 0.1349419802427292, 0.6918326020240784, 0.44226399064064026, -0.27654755115509033, -0.31416380405426025, 0.6921458840370178, 0.34632331132888794, -0.041358280926942825, 0.31910157203674316, 0.13670523464679718, -0.04609650745987892, -0.26573842763900757, -0.46046197414398193, -0.17474311590194702, -0.010774786584079266, 0.21124546229839325, -0.2506549656391144, 0.05266217514872551, 0.26425328850746155, -0.09295502305030823, -0.34485167264938354, -0.57659912109375, -0.002637488767504692, -0.30858248472213745, -0.19747228920459747, 0.005446853581815958, 0.5021294951438904, -0.17439152300357819, 0.1913726031780243, -0.22889888286590576, -0.2599051296710968, 0.545295238494873, -0.5809483528137207, 0.9059168696403503, -0.16381891071796417, -0.08430704474449158, -0.29159361124038696, 0.26130563020706177, -0.453090637922287, -0.5860328674316406, -0.18445229530334473, -0.7905458807945251, 0.5145899057388306, 0.30674776434898376, -0.15665078163146973, -0.010274163447320461, -0.2826630771160126, -0.17753750085830688, 0.08746267855167389, 0.4176737666130066, -1.6535612344741821, 0.20465010404586792, 0.5176762342453003, -0.19286905229091644, 0.6551369428634644, -0.2550574541091919, -0.3057389557361603, 0.5545822381973267, -0.3434443771839142, 0.09070255607366562, -0.4838918447494507, -0.0054054781794548035, -0.3305385410785675, 0.2940455973148346, 0.08882751315832138, -0.04194898158311844, 0.1241106316447258, -0.3534480333328247, -0.3736811876296997, 0.30397486686706543, 0.004519172012805939, 0.2748650014400482, 0.17399586737155914, -0.09785371273756027, -0.1855577677488327, -0.2281871885061264, -0.21976259350776672, 0.7101989984512329, -0.4327967166900635, 0.27629390358924866, 0.1662922501564026, -0.1638050228357315, -0.4014763832092285, -0.09098920971155167, 0.49464520812034607, 0.43304771184921265, 0.32080918550491333, 0.06274984776973724, 0.8179517388343811, 0.5851423740386963, -0.226453959941864, 0.39161908626556396, -0.02347426861524582, 0.4228699207305908, 0.2722546458244324, 0.10526186227798462, -0.04303229972720146, 0.4490645229816437, 0.6480507254600525, -0.48197805881500244, -0.09460679441690445, 0.12205280363559723, -0.5069171786308289, -0.7493430972099304, 0.3993034362792969, -0.13829606771469116, -0.310914009809494, 0.3234768807888031, -0.3182300627231598, 0.09234993904829025, -0.2417997121810913, 0.1798134744167328, -0.638672411441803, -0.05771524831652641, -0.28006115555763245, -0.44104447960853577, 0.12093167752027512, 0.0769425481557846, -0.010583163239061832, 0.6732715964317322, 0.5427714586257935, 0.5353928804397583, -0.6006384491920471, -0.22127994894981384, -0.12787437438964844, 0.3620242476463318, 0.06013040617108345, 0.11181006580591202, 0.27209627628326416, -0.20955464243888855, 0.34593018889427185, -0.807579755783081, -0.5775582194328308, 0.5409204363822937, -0.02873731218278408, 0.24082021415233612, -0.13981005549430847, -0.05797017738223076, 0.11740408837795258, 0.22988170385360718, -0.5531104207038879, -0.6847423315048218, 0.2649863660335541, 0.2672853469848633, 0.3451954126358032, -0.10093766450881958, 0.1745494306087494, -0.1915750950574875, 0.06951170414686203, -0.033979158848524094, -0.24006059765815735, 0.25452470779418945, 0.5313581228256226, -0.013443672098219395, 0.6373400688171387, 0.37523749470710754, 0.14931848645210266, 0.26657432317733765, -0.6284800171852112, -0.3389529287815094, 0.26048529148101807, 0.1442587524652481, -0.19539713859558105, -0.31131890416145325, 0.20769435167312622, -0.15146562457084656, 0.38622474670410156, -0.14692434668540955, 2.16040301322937, 0.2892966866493225, 0.16240957379341125, -0.39856451749801636, 0.5663319826126099, -0.09896737337112427, 0.1805577427148819, -0.08840185403823853, -0.2883470058441162, 0.21962928771972656, -0.09272915124893188, 0.2519668936729431, 4.958240970154293e-05, 0.23210066556930542, 0.5099530816078186, 0.5288278460502625, -0.14586661756038666, -0.4939904510974884, -0.42668256163597107, -0.04806998372077942, -0.3960345387458801, -0.06693911552429199, 0.33651864528656006, 0.0003529983514454216, -0.20948028564453125, 0.07369456440210342, 0.07899042963981628, -0.18911314010620117, 0.25403669476509094, 0.396759033203125, -0.7564601302146912, -0.035524725914001465, 0.5711250901222229, 0.5872853994369507, -0.24341456592082977, 0.07278706133365631, 0.232346311211586, -0.44576138257980347, 0.059212349355220795, -0.008786634542047977, -0.24360725283622742, -0.6272181272506714, 0.6675294637680054, 0.18302366137504578, 0.35254597663879395, 0.12698577344417572, -0.07981990277767181, -0.18744252622127533, 0.7362368702888489, -0.00964146014302969, -0.2995283901691437, -0.13315461575984955, -0.2723553478717804, 0.15739375352859497, 0.20337805151939392, 0.08520163595676422, -0.13200326263904572, -0.5903628468513489, -0.3395122289657593, 0.09871797263622284, -0.41703662276268005, 0.42235442996025085, 0.1742190569639206, -0.2577683627605438, -0.0725637823343277, 0.11506867408752441, -0.37862229347229004, 0.0073034199886024, 0.14432720839977264, -0.11842063814401627, 0.15290383994579315, 0.5317602157592773, -0.008331174962222576, 0.013400676660239697, 0.5127222537994385, 0.18407192826271057, 0.228047177195549, -0.28993460536003113, -0.2626085579395294, -3.236173152923584, 0.1706666499376297, 0.25422558188438416, -0.18305911123752594, -0.08924354612827301, 0.019216811284422874, 0.059890273958444595, -0.1317589432001114, 0.08469528704881668, -0.7019630670547485, 0.16164611279964447, 0.30405664443969727, -0.12850019335746765, -0.08189859241247177, 0.17561641335487366, -0.22100894153118134, 0.40156880021095276, -0.4562336802482605, -0.556627631187439, -0.33463501930236816, 0.030371762812137604, 0.3819870054721832, -0.23649631440639496, -0.23940223455429077, -0.1142936423420906, 0.03333212062716484, 0.5141474604606628, -0.3797993063926697, 0.06257864832878113, 0.04985616356134415, -0.09762069582939148, -0.030977386981248856, -0.012592471204698086, -0.1346411556005478, 0.20987637341022491, 0.01427067443728447, -0.545782744884491, -0.05716570466756821, 0.2080068290233612, -0.061954546719789505, 0.1259821653366089, 0.37951770424842834, -0.4688016176223755, -0.07125554233789444, -0.07596952468156815, -0.2462599277496338, 0.4076462686061859, -0.42994198203086853, 0.707909882068634, -0.061874035745859146, 0.28605416417121887, -0.07345134764909744, 0.1882917433977127, -0.15784277021884918, 0.18654629588127136, 0.29787424206733704, 0.4403696060180664, -0.0010919725755229592, 0.08094488084316254, -0.4952464997768402, 0.5117387175559998, -0.15489862859249115, -0.2530190944671631, -0.012920659966766834, 0.30635660886764526, -0.3816797137260437, 0.015753531828522682, 0.18933629989624023, 0.10030578821897507, -0.03963802009820938, -0.14209158718585968, 0.07355976104736328, 0.18117882311344147, 0.33587589859962463, 0.00099424016661942, -0.07707319408655167, 0.4239234924316406, 0.15456250309944153, 0.5243333578109741, -0.026983879506587982, -0.12279278039932251, -0.021700754761695862, -0.33382365107536316, 0.2140650898218155, 0.11083193123340607, -7.167384147644043, -0.38900530338287354, -0.05917663499712944, -0.17394766211509705, 0.3633168637752533, -0.49448254704475403, -0.13882599771022797, -0.5048572421073914, 0.14011603593826294, -0.08674301952123642, 0.3350716531276703, 0.2013920545578003, -0.3757869005203247, -0.7621421813964844, 0.5274125933647156, 0.22410990297794342]</t>
+          <t>['medium', 'medium', 'medium', 'high', 'high', 'high']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>[-0.5, -0.5, 0.5, 0.5, -0.5, -1.0]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 4, 5, 4]</t>
+          <t>[35.0, 30.0, 35.0, 40.0, 40.0, 30.0]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['woman', 'woman', 'man', 'man', 'man', 'man']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>[35.0, 30.0, 35.0, 40.0, 40.0, 30.0]</t>
+          <t>[1, 1, 1, 2, 5, 3]</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>['woman', 'woman', 'man', 'man', 'man', 'man']</t>
+          <t>[4, 4, 4, 3, 5, 5]</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 5, 3]</t>
+          <t>[3, 2, 5, 4, 5, 5]</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>[4, 4, 4, 3, 5, 5]</t>
+          <t>[3, 5, 5, 4, 5, 4]</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>[3, 2, 5, 4, 5, 5]</t>
+          <t>[1, 1, 3, 2, 2, 1]</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>[3, 5, 5, 4, 5, 4]</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>[1, 1, 3, 2, 2, 1]</t>
-        </is>
+          <t>[3, 1, 5, 4, 5, 5]</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>6</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>[3, 1, 5, 4, 5, 5]</t>
+          <t>[3, 2, 5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>[3, 2, 5, 5, 5, 5]</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
           <t>[0.         0.16666667 0.16666667 0.         0.66666667]</t>
         </is>
       </c>
-      <c r="T9" t="n">
+      <c r="S9" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -1325,85 +1264,78 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[2, 4, 1, 2, 3, 2]</t>
+          <t>['{}', '{}', '{}', '{}', 'none', '{}']</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['{}', '{}', '{}', '{}', 'none', '{}']</t>
+          <t>['left', 'far left', 'center', 'right', 'center', 'left']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[0.6042274236679077, 0.4851360023021698, -0.24037162959575653, -0.5280382037162781, -0.22253260016441345, -0.46449923515319824, 0.5265598893165588, 0.5716187357902527, -0.2087571918964386, -0.3453870713710785, 0.10044242441654205, -0.017152294516563416, -0.1403307020664215, 0.6785656213760376, 0.30523714423179626, -0.08180639892816544, -0.2935158908367157, 0.34274423122406006, -0.035849109292030334, 0.19257214665412903, -0.31111565232276917, -0.054798971861600876, 0.02989109605550766, -0.2691267430782318, -0.5055041313171387, -0.267416387796402, -0.1505761593580246, -0.0424509234726429, -0.1033293604850769, -0.18858765065670013, 0.13031679391860962, 0.22428672015666962, -0.0924828052520752, -0.3667428195476532, 0.6267938017845154, 0.27734169363975525, 0.09395883977413177, -0.18712563812732697, -0.1456613391637802, 0.030498351901769638, 0.0274529829621315, -0.09762481600046158, 0.3812287747859955, -0.08851145952939987, -0.0681697204709053, -0.1567869782447815, -2.799598217010498, -0.18515974283218384, -0.07424431294202805, -0.308572381734848, 0.5240286588668823, -0.3294767141342163, -0.20419971644878387, 0.046662453562021255, 0.3920004367828369, 0.23793435096740723, -0.1723371148109436, 0.11655691266059875, 0.30315834283828735, 0.36248570680618286, 0.3354548215866089, 0.3480813205242157, 0.07674938440322876, 0.41965121030807495, 0.05435658246278763, 0.09229353070259094, 0.372767835855484, 0.6895819306373596, -0.3671171963214874, 0.6717217564582825, -0.7017413377761841, -0.11955191940069199, 0.22153885662555695, -0.20504844188690186, 0.33713945746421814, -0.29613155126571655, -0.012671113014221191, 0.5715284943580627, -0.1337185651063919, -0.14029647409915924, -0.19466303288936615, 0.2571083605289459, 0.10229097306728363, -0.19366629421710968, 0.044923704117536545, 0.7740790247917175, -0.6623068451881409, -0.13103856146335602, 0.5689128637313843, 0.3259016275405884, -0.13891541957855225, 0.36093080043792725, -0.033771246671676636, -0.048743605613708496, 0.3242141008377075, 0.09394975006580353, 0.1673993468284607, 0.45065343379974365, 0.44060465693473816, 0.10351526737213135, 0.6610032916069031, 0.185176819562912, 0.11248841881752014, -0.3928033411502838, 0.44415774941444397, -0.24528129398822784, -0.1251276284456253, -0.4745287597179413, 0.1873224377632141, -2.5874829292297363, 0.520758330821991, 0.11676786094903946, -0.5445818305015564, -0.618729829788208, -0.035324618220329285, 0.6540350914001465, 0.5663493275642395, -0.03456425666809082, 0.547351598739624, 0.2854467034339905, -0.2730134427547455, 0.056448303163051605, -0.22182095050811768, 0.035564858466386795, 0.24296480417251587, 0.21027693152427673, 0.2696702182292938, -0.14307352900505066, 0.29935047030448914, 0.14086420834064484, 0.2264181524515152, 0.6315137147903442, 0.09260699898004532, -0.4010661244392395, -0.3853483200073242, 0.07450044900178909, 0.18970410525798798, -0.37857773900032043, -0.08862239122390747, -0.1290733963251114, -0.4547671675682068, -0.7306509613990784, -3.3803422451019287, 0.5048614144325256, 0.09933124482631683, 0.21538063883781433, -0.2851168215274811, 3.884852412738837e-05, 0.04365021362900734, 0.19881674647331238, 0.22738699615001678, -0.08633432537317276, 0.21766047179698944, 0.21966740489006042, -0.007763764820992947, -0.11791069060564041, -0.3947746455669403, -0.3780047595500946, 0.3906230330467224, 0.5448205471038818, 0.5809876322746277, -0.5093445777893066, -0.010524091310799122, 0.2632623016834259, -0.049977488815784454, 0.013404658995568752, 0.6624396443367004, 0.32752394676208496, -0.013064281083643436, -0.2634504437446594, -0.2275594025850296, 0.22461256384849548, 0.605030357837677, 0.08393813669681549, -0.15269935131072998, -0.1541038155555725, 0.42137157917022705, 0.31355658173561096, -0.11290012300014496, -0.3257770538330078, -0.6344757080078125, 0.10940181463956833, 0.06481203436851501, 0.17227235436439514, 0.8271979689598083, -0.12440114468336105, 0.6068388819694519, -0.16187670826911926, -0.375459223985672, 0.45427167415618896, -0.3149215579032898, -0.16291432082653046, 0.5618054270744324, 0.39582470059394836, 0.45634278655052185, -0.37393462657928467, 0.2161281853914261, -0.8137587904930115, -0.08662495017051697, 0.2982008159160614, -0.1062602624297142, -0.0013419337337836623, -0.30853691697120667, 0.2594192922115326, -0.1527462750673294, 3.8799831867218018, 0.029075855389237404, -0.3785647749900818, 0.18582940101623535, 0.4730794429779053, -0.3833707571029663, -0.4706297814846039, -0.15288157761096954, -0.15946842730045319, -0.2615560293197632, 0.22312723100185394, 0.6767536401748657, 0.010286644101142883, -0.6127915978431702, -0.036375466734170914, 0.13225173950195312, 0.3437627851963043, -0.155336394906044, 0.5013025999069214, -0.03344014659523964, -0.2653759717941284, -0.040953174233436584, 0.4733760356903076, -0.06348954886198044, -2.2907705307006836, 0.2626836597919464, -0.00659785233438015, -0.30113404989242554, 0.16906994581222534, -0.07815973460674286, 0.3862297236919403, -0.06149161607027054, -0.3897690176963806, 0.035573434084653854, 0.08319545537233353, 0.29060643911361694, 0.09740735590457916, -0.05805964767932892, 0.10992731899023056, -0.11052168160676956, 0.4079328775405884, -0.14651156961917877, -0.07894629240036011, -0.10737816244363785, 0.10902183502912521, 0.20043767988681793, 0.040058355778455734, 0.14215269684791565, -0.17496252059936523, -0.005160209722816944, -0.005314487963914871, 0.18935830891132355, -0.023090623319149017, -0.7454828023910522, -0.3367000222206116, -0.25713515281677246, 0.21868054568767548, 0.5903019905090332, 0.2714700698852539, -0.6390297412872314, -0.34694603085517883, 0.4397168457508087, -0.32003065943717957, -0.4259476363658905, -0.22455774247646332, 0.14707151055335999, -0.3166290819644928, -0.09525907784700394, -3.136013984680176, 0.27587196230888367, 0.17771746218204498, 0.014656432904303074, -0.17750658094882965, -0.08551173657178879, -0.12184806913137436, 0.43624284863471985, 0.18853484094142914, -0.7644718289375305, 0.5489007234573364, 0.4378930628299713, -0.12132789939641953, 0.6259509921073914, -0.045677538961172104, 0.2127670794725418, 0.0953408032655716, 0.2400176227092743, -0.365387886762619, -0.3737383782863617, 0.5503791570663452, 0.2818879783153534, -0.44611096382141113, 0.42100629210472107, 0.07345400005578995, 0.01102551817893982, -0.013067331165075302, -0.07631528377532959, 0.49405431747436523, -0.22327420115470886, 0.3731691539287567, -0.22760267555713654, -0.13305869698524475, 0.05796993523836136, -0.828317403793335, -2.9163410663604736, 0.018156183883547783, -0.21793542802333832, -0.3445959687232971, -0.2704177796840668, 0.09103895723819733, 0.3465747535228729, -0.3206803500652313, -0.7453615665435791, 0.230447456240654, 0.1433979570865631, 0.184391051530838, 0.23681682348251343, 0.10497236996889114, 0.3625425696372986, 0.249495729804039, 0.417483389377594, -0.27590781450271606, 0.5301280617713928, 0.32736271619796753, -0.1305910348892212, 0.401480495929718, -0.19907836616039276, 0.24871507287025452, -0.05063857510685921, 0.5842112898826599, -0.3772759437561035, 0.03050808236002922, 0.026003453880548477, 0.2142380177974701, -0.2331048995256424, -0.38433173298835754, -0.3671887516975403, -0.10892970114946365, -0.2550339996814728, -0.15509125590324402, -0.03653523698449135, 0.19151535630226135, 0.4899614751338959, -0.17594346404075623, 0.32216930389404297, 0.5188902020454407, -0.013008210808038712, 0.5379699468612671, 0.7187414765357971, -0.17149296402931213, 0.31449761986732483, 0.0392008014023304, -0.037685878574848175, 0.14744921028614044, -0.5819541811943054, 0.079169861972332, 0.8901492357254028, 0.007037466391921043, -0.2299395650625229, -0.13396628201007843, 0.3877056837081909, 0.32153549790382385, 0.07774927467107773, 0.2671356499195099, 0.593773603439331, -0.3456266224384308, 0.5045838356018066, -0.05535459145903587, 0.15692339837551117, -0.4949079751968384, 0.192511647939682, -0.8074871897697449, 0.07035255432128906, 0.1184888407588005, -0.10099881887435913, 0.26660341024398804, -0.27112069725990295, -1.2494384050369263, -0.26059097051620483, 0.034450653940439224, -0.45202314853668213, 0.5256689786911011, 0.10992826521396637, 0.0167691707611084, -0.27736419439315796, -0.006018148735165596, -0.5031956434249878, 0.4911349415779114, -0.7254021763801575, -0.49148836731910706, -0.08809302002191544, 0.0874016135931015, -0.0525771863758564, 0.1048455759882927, -0.2787945568561554, 0.4306076467037201, -0.5004633665084839, 0.19746316969394684, -0.40646442770957947, 0.1410662978887558, 0.10290701687335968, -0.8170720934867859, 0.19394995272159576, -0.01246240921318531, -0.21950271725654602, -0.4870717227458954, 0.017187561839818954, -0.06795790046453476, -0.1391603797674179, -0.12118654698133469, -0.22791574895381927, -0.0025971673894673586, -0.17063432931900024, 0.3884946405887604, -0.12377586215734482, -0.22715339064598083, 0.09233680367469788, 0.46107056736946106, 0.5101954340934753, -0.2366076111793518, -0.37602829933166504, 0.7361128926277161, 0.1020706444978714, -0.008448746055364609, 0.3906968832015991, 0.1443820744752884, -0.047125350683927536, -0.49141108989715576, -0.18750014901161194, -0.1452484130859375, 0.28909504413604736, -0.31017768383026123, -0.3199327886104584, -0.43382611870765686, 0.11193878203630447, 0.0061812372878193855, -0.45073801279067993, -0.2724973261356354, -0.0768909901380539, -0.07836123555898666, -0.6039547920227051, -0.051489707082509995, 0.1807176172733307, 0.47430193424224854, 0.27547338604927063, 0.14400997757911682, -0.4734775722026825, 0.03690943494439125, -0.09567881375551224, 0.8349630832672119, -0.21115265786647797, -0.020571209490299225, -0.16846273839473724, 0.667644202709198, -0.022514287382364273, -0.544336199760437, -0.2665042579174042, -0.8539516925811768, 0.12006784975528717, 0.42973968386650085, -0.14730222523212433, 0.2071104198694229, -0.12986789643764496, -0.04241425171494484, 0.4739196300506592, 0.23184040188789368, -1.7273621559143066, 0.5215877294540405, 1.1158435344696045, 0.043027665466070175, 0.189073845744133, 0.2996356189250946, -0.7225369215011597, 0.4213525354862213, 0.12231208384037018, 0.2951870858669281, -0.31043991446495056, 0.2747855484485626, 0.09371314942836761, 0.08526313304901123, 0.19931718707084656, 0.3547922670841217, 0.22638462483882904, -0.7375215291976929, 0.03679627552628517, -0.235737606883049, 0.21743963658809662, 0.14895881712436676, -0.09582548588514328, -0.07298259437084198, -0.3551340103149414, -0.40845513343811035, 0.020597314462065697, 0.4637007713317871, -0.10319489985704422, 0.725358247756958, 0.13993951678276062, -0.3470160663127899, -0.7139071226119995, -0.34150877594947815, 0.205216184258461, 0.16845260560512543, 0.23416297137737274, 0.01677868887782097, 0.5821306109428406, 0.8509241342544556, -0.25498008728027344, 0.5415651798248291, 0.5483371615409851, -0.146758571267128, 0.22837691009044647, 0.20254622399806976, -0.08559687435626984, 0.7170289754867554, 0.28345322608947754, -0.6043246388435364, -0.19414430856704712, -0.08102928847074509, -0.4134349524974823, -0.30198991298675537, 0.15085889399051666, -0.14167948067188263, -0.004838617518544197, 0.0423458106815815, -0.374694287776947, 0.04566779360175133, -0.1730050891637802, -0.16325214505195618, -0.6603958606719971, -0.059810299426317215, -0.37070533633232117, -0.1297290325164795, 0.22211281955242157, -0.5182220935821533, -0.24653875827789307, 0.4794231951236725, 0.9189571142196655, 0.25826725363731384, -0.5144426822662354, 0.2409961074590683, -0.4512054920196533, 0.3683679699897766, 0.32643604278564453, 0.5833449959754944, 0.6406819820404053, 0.034548401832580566, 0.15068501234054565, -0.7893508672714233, 0.2710447609424591, 0.29313355684280396, 0.15181022882461548, 0.2991618812084198, -0.12109576910734177, -0.2145492285490036, 0.04695790633559227, -0.47151753306388855, -0.5326614379882812, -0.5847060680389404, 0.38720303773880005, -0.04887855425477028, 0.38097837567329407, 0.4151987135410309, 0.19760186970233917, -0.31901031732559204, 0.2622964084148407, -0.11286980658769608, -0.19085879623889923, 0.3347975015640259, 0.5561801791191101, 0.3239700198173523, 0.027024423703551292, 0.28627026081085205, 0.3816852271556854, 0.3525294363498688, -0.5734255313873291, -0.50982266664505, 0.02143029496073723, -0.08640342205762863, -0.39468133449554443, -0.31488415598869324, 0.13451915979385376, -0.6433650255203247, 0.16712002456188202, -0.3023641109466553, 2.010913848876953, 0.46767911314964294, -0.030924580991268158, -0.6253504753112793, 0.5756930708885193, -0.11840906739234924, -0.07732848823070526, 0.25721821188926697, -0.21819941699504852, 0.04227522388100624, -0.260029137134552, 0.2535555958747864, 0.033734895288944244, 0.31398266553878784, 0.3253995478153229, 0.42515328526496887, -0.37924930453300476, -0.3323740065097809, -0.6188485026359558, -0.1280844658613205, -0.04356098920106888, -0.14999571442604065, 0.26939988136291504, -0.5144818425178528, -0.12548097968101501, 0.551857054233551, -0.10448715090751648, 0.1423729658126831, 0.09885921329259872, 0.25196048617362976, -0.26065418124198914, -0.21184417605400085, 0.011878342367708683, 0.28484979271888733, -0.31256619095802307, -0.15730568766593933, 0.26247072219848633, -0.5835923552513123, 0.19501136243343353, 0.07083580642938614, -0.5060252547264099, -0.46629229187965393, 0.5700942873954773, 0.12752215564250946, 0.23591622710227966, 0.34017422795295715, -0.36945876479148865, 0.25876837968826294, 0.5080874562263489, 0.28064075112342834, 0.07446656376123428, -0.2814546823501587, -0.6407853364944458, 0.15288379788398743, 0.14214038848876953, 0.027266250923275948, 0.3285443186759949, -0.21004749834537506, -0.1862725466489792, -0.17834700644016266, -0.5113751888275146, 0.1906040757894516, 0.48688405752182007, 0.24127686023712158, -0.5397933125495911, 0.40942394733428955, -0.5792311429977417, -0.27343472838401794, -0.15141861140727997, -0.5175623893737793, 0.40312185883522034, 0.4760286509990692, 0.6154736876487732, -0.27396735548973083, 0.3016008734703064, 0.014282799325883389, 0.18507902324199677, -0.3722776174545288, -0.5082061290740967, -2.7680156230926514, 0.359542578458786, -0.33995306491851807, -0.2359429895877838, 0.11912500113248825, -0.07698272913694382, 0.3355603516101837, 0.2395051270723343, 0.2177371382713318, -0.01397741585969925, 0.05948018655180931, 0.3969450891017914, 0.6527794599533081, 0.08472593128681183, 0.30155476927757263, -0.10231318324804306, 0.015279905870556831, -0.567619800567627, -0.22007574141025543, -0.31948167085647583, 0.05779685080051422, 0.15039461851119995, 0.08788231760263443, -0.41367608308792114, -0.5465407371520996, 0.34021222591400146, 0.05078602209687233, -0.12810787558555603, 0.39097821712493896, 0.2664864957332611, -0.3082010746002197, 0.5644044280052185, -0.09985516220331192, -0.30615663528442383, -0.23279309272766113, -0.018992222845554352, -0.38009920716285706, 0.027349384501576424, 0.003440568223595619, 0.04369015619158745, -0.2781481444835663, 0.42960843443870544, -0.22491253912448883, 0.09208428859710693, 0.2862774133682251, -0.2453400045633316, 0.5331147313117981, -0.39570704102516174, 0.6686719059944153, -0.49566832184791565, 0.07974754273891449, -0.15706083178520203, 0.32763177156448364, 0.27635350823402405, 0.3781832456588745, -0.24763132631778717, 0.2599342167377472, 0.27099648118019104, 0.07547719031572342, -0.5321049690246582, -0.006321737077087164, 0.3232170045375824, -0.1663064956665039, -0.09078129380941391, 0.14803995192050934, 0.06622032821178436, 0.04179409518837929, 0.18605579435825348, -0.0553361177444458, -0.12194746732711792, -0.15212172269821167, -0.35968804359436035, 0.3040003776550293, -0.18691951036453247, -0.09126021713018417, -0.38201904296875, 0.24608184397220612, 0.7252181172370911, 0.44190749526023865, -0.16702377796173096, -0.07804721593856812, 0.10614373534917831, -0.4217165410518646, 0.008793061599135399, 0.06259702891111374, -6.918983459472656, -0.07237349450588226, -0.15822093188762665, -0.2941526770591736, 0.18648260831832886, -0.30558887124061584, 0.3200792074203491, -0.35361552238464355, 0.007853090763092041, -0.4752953052520752, 0.3237743377685547, -0.0214448980987072, -0.363576740026474, -0.06417877227067947, 0.4503228962421417, 0.6206876635551453]</t>
+          <t>['high', 'high', 'high', 'medium', 'high', 'high']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>[-0.5, -1.0, 0.0, 0.5, 0.0, -0.5]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[4, 5, 5, 3, 5, 5]</t>
+          <t>[40.0, 25.0, 40.0, 35.0, 45.0, 35.0]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['woman', 'woman', 'woman', 'woman', 'woman', 'woman']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>[40.0, 25.0, 40.0, 35.0, 45.0, 35.0]</t>
+          <t>[1, 3, 1, 1, 4, 1]</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>['woman', 'woman', 'woman', 'woman', 'woman', 'woman']</t>
+          <t>[4, 5, 5, 5, 1, 5]</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>[1, 3, 1, 1, 4, 1]</t>
+          <t>[2, 3, 1, 1, 2, 2]</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>[4, 5, 5, 5, 1, 5]</t>
+          <t>[2, 5, 5, 5, 5, 4]</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>[2, 3, 1, 1, 2, 2]</t>
+          <t>[1, 4, 1, 3, 3, 1]</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>[2, 5, 5, 5, 5, 4]</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>[1, 4, 1, 3, 3, 1]</t>
-        </is>
+          <t>[1, 3, 1, 1, 1, 1]</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>6</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>[1, 3, 1, 1, 1, 1]</t>
+          <t>[3, 3, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>[3, 3, 1, 1, 2, 1]</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
           <t>[0.5        0.16666667 0.33333333 0.         0.        ]</t>
         </is>
       </c>
-      <c r="T10" t="n">
+      <c r="S10" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
